--- a/testcases/货架偏移容差测试用例.xlsx
+++ b/testcases/货架偏移容差测试用例.xlsx
@@ -8005,7 +8005,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="16.5" customHeight="1">
       <c r="A3" s="17" t="inlineStr">
         <is>
@@ -8594,7 +8593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:P66"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="0"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8672,6 +8671,36 @@
           <t>备注</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>实际结果</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>测试人员</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>BugID</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Bug频率</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>问题时间</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>执行时间</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
@@ -8704,10 +8733,29 @@
           <t>基准</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr"/>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H4" s="9" t="inlineStr"/>
       <c r="I4" s="9" t="inlineStr"/>
       <c r="J4" s="9" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>直接写入原始文件ok</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2026-07-05 10:23:57</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -10808,7 +10856,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="16.5" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>

--- a/testcases/货架偏移容差测试用例.xlsx
+++ b/testcases/货架偏移容差测试用例.xlsx
@@ -8753,7 +8753,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-07-05 10:23:57</t>
+          <t>2026-07-05 20:40:41</t>
         </is>
       </c>
     </row>
@@ -8788,10 +8788,24 @@
           <t>基准</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr"/>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
       <c r="H5" s="9" t="inlineStr"/>
       <c r="I5" s="9" t="inlineStr"/>
       <c r="J5" s="9" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2026-07-05 20:42:45</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2026-07-05 20:42:49</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
@@ -8824,10 +8838,19 @@
           <t>基准</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr"/>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="H6" s="9" t="inlineStr"/>
       <c r="I6" s="9" t="inlineStr"/>
       <c r="J6" s="9" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2026-07-05 20:42:54</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">

--- a/testcases/货架偏移容差测试用例.xlsx
+++ b/testcases/货架偏移容差测试用例.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27950" windowHeight="12400" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="19240" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="货架偏移容差测试用例" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="偏移场景说明" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="统计汇总" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="测试记录表(填写用)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="判定标准与执行说明" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="货架偏移容差测试用例" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="偏移场景说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="统计汇总" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试记录表(填写用)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="判定标准与执行说明" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'货架偏移容差测试用例'!$A$3:$U$66</definedName>
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="29">
+  <fonts count="28">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -82,13 +82,6 @@
       <i val="1"/>
       <color rgb="FF2F5496"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
@@ -495,7 +488,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -516,19 +509,6 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -664,29 +644,32 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="5" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
@@ -695,122 +678,119 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="7" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="8" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="8" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="9" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="7" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="8" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="9" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="10" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="38" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="39" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="40" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="41" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="41" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="42" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="42" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="43" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="43" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -836,19 +816,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -888,8 +861,7 @@
     <xf numFmtId="0" fontId="4" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1302,11 +1274,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U66"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="0"/>
+  <dimension ref="A1:AA66"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" style="19" min="2" max="2"/>
+    <col width="7" customWidth="1" style="18" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -1333,7 +1305,7 @@
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="20" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>测试目标: 验证实际货架偏移10cm/3°后,机器人能否容差匹配成功到达货架位置 | 判定标准: 不碰撞+成功停靠=Pass | 偏移含义: 物理货架被偏移放置,地图位置未更新</t>
         </is>
@@ -1445,9 +1417,39 @@
           <t>备注</t>
         </is>
       </c>
+      <c r="V3" s="28" t="inlineStr">
+        <is>
+          <t>测试结果</t>
+        </is>
+      </c>
+      <c r="W3" s="28" t="inlineStr">
+        <is>
+          <t>测试人员</t>
+        </is>
+      </c>
+      <c r="X3" s="28" t="inlineStr">
+        <is>
+          <t>BugID</t>
+        </is>
+      </c>
+      <c r="Y3" s="28" t="inlineStr">
+        <is>
+          <t>Bug频率</t>
+        </is>
+      </c>
+      <c r="Z3" s="28" t="inlineStr">
+        <is>
+          <t>问题时间</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>执行时间</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="60" customHeight="1">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>TC-OFF-001</t>
         </is>
@@ -1457,74 +1459,74 @@
           <t>S1</t>
         </is>
       </c>
-      <c r="C4" s="21" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
         <is>
           <t>小货架</t>
         </is>
       </c>
-      <c r="D4" s="21" t="inlineStr">
+      <c r="D4" s="20" t="inlineStr">
         <is>
           <t>0.76×0.5m</t>
         </is>
       </c>
-      <c r="E4" s="21" t="inlineStr">
+      <c r="E4" s="20" t="inlineStr">
         <is>
           <t>无偏移(基准)</t>
         </is>
       </c>
-      <c r="F4" s="21" t="inlineStr">
+      <c r="F4" s="20" t="inlineStr">
         <is>
           <t>货架位置与地图完全一致,无偏移</t>
         </is>
       </c>
-      <c r="G4" s="21" t="inlineStr">
+      <c r="G4" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H4" s="21" t="inlineStr">
+      <c r="H4" s="20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I4" s="22" t="inlineStr">
+      <c r="I4" s="21" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="J4" s="23" t="inlineStr">
+      <c r="J4" s="22" t="inlineStr">
         <is>
           <t>基准</t>
         </is>
       </c>
-      <c r="K4" s="21" t="inlineStr">
+      <c r="K4" s="20" t="inlineStr">
         <is>
           <t>导航至货架位置,停靠精度±5cm内</t>
         </is>
       </c>
-      <c r="L4" s="21" t="inlineStr">
+      <c r="L4" s="20" t="inlineStr">
         <is>
           <t>路径规划正常,无异常绕行</t>
         </is>
       </c>
-      <c r="M4" s="21" t="inlineStr">
+      <c r="M4" s="20" t="inlineStr">
         <is>
           <t>到达货架后，ROS自动修正匹配路径，稳定后退进入货架下，不会触发避障调整</t>
         </is>
       </c>
-      <c r="N4" s="21" t="inlineStr">
+      <c r="N4" s="20" t="inlineStr">
         <is>
           <t>匹配成功:机器人到达货架位置并完成停靠</t>
         </is>
       </c>
-      <c r="O4" s="21" t="inlineStr">
+      <c r="O4" s="20" t="inlineStr">
         <is>
           <t>1. 小货架(0.76×0.5m)摆放至地图标记位置
 2. APP下发标准货架尺寸配置
 3. 机器人已建图并定位</t>
         </is>
       </c>
-      <c r="P4" s="21" t="inlineStr">
+      <c r="P4" s="20" t="inlineStr">
         <is>
           <t>1. APP下发导航任务至小货架位置
 2. 机器人导航至目标点
@@ -1534,18 +1536,40 @@
 6. 检查是否碰撞</t>
         </is>
       </c>
-      <c r="Q4" s="21" t="inlineStr"/>
-      <c r="R4" s="21" t="inlineStr"/>
-      <c r="S4" s="21" t="inlineStr"/>
-      <c r="T4" s="21" t="inlineStr"/>
-      <c r="U4" s="21" t="inlineStr">
+      <c r="Q4" s="20" t="inlineStr">
+        <is>
+          <t>12138</t>
+        </is>
+      </c>
+      <c r="R4" s="20" t="inlineStr"/>
+      <c r="S4" s="20" t="inlineStr"/>
+      <c r="T4" s="20" t="inlineStr"/>
+      <c r="U4" s="20" t="inlineStr">
         <is>
           <t>基准用例,必须全部Pass才能继续偏移测试</t>
         </is>
       </c>
+      <c r="V4" s="28" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="W4" s="28" t="inlineStr">
+        <is>
+          <t>吴晓峰</t>
+        </is>
+      </c>
+      <c r="X4" s="28" t="n"/>
+      <c r="Y4" s="28" t="n"/>
+      <c r="Z4" s="28" t="n"/>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-06 01:09:56</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>TC-OFF-002</t>
         </is>
@@ -1555,74 +1579,74 @@
           <t>S2</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>中货架A</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>0.8×0.85m</t>
         </is>
       </c>
-      <c r="E5" s="21" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>无偏移(基准)</t>
         </is>
       </c>
-      <c r="F5" s="21" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>货架位置与地图完全一致,无偏移</t>
         </is>
       </c>
-      <c r="G5" s="21" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H5" s="21" t="inlineStr">
+      <c r="H5" s="20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I5" s="22" t="inlineStr">
+      <c r="I5" s="21" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="J5" s="23" t="inlineStr">
+      <c r="J5" s="22" t="inlineStr">
         <is>
           <t>基准</t>
         </is>
       </c>
-      <c r="K5" s="21" t="inlineStr">
+      <c r="K5" s="20" t="inlineStr">
         <is>
           <t>导航至货架位置,停靠精度±5cm内</t>
         </is>
       </c>
-      <c r="L5" s="21" t="inlineStr">
+      <c r="L5" s="20" t="inlineStr">
         <is>
           <t>路径规划正常,无异常绕行</t>
         </is>
       </c>
-      <c r="M5" s="21" t="inlineStr">
+      <c r="M5" s="20" t="inlineStr">
         <is>
           <t>到达货架后，ROS自动修正匹配路径，稳定后退进入货架下，不会触发避障调整</t>
         </is>
       </c>
-      <c r="N5" s="21" t="inlineStr">
+      <c r="N5" s="20" t="inlineStr">
         <is>
           <t>匹配成功:机器人到达货架位置并完成停靠</t>
         </is>
       </c>
-      <c r="O5" s="21" t="inlineStr">
+      <c r="O5" s="20" t="inlineStr">
         <is>
           <t>1. 中货架A(0.8×0.85m)摆放至地图标记位置
 2. APP下发标准货架尺寸配置
 3. 机器人已建图并定位</t>
         </is>
       </c>
-      <c r="P5" s="21" t="inlineStr">
+      <c r="P5" s="20" t="inlineStr">
         <is>
           <t>1. APP下发导航任务至中货架A位置
 2. 机器人导航至目标点
@@ -1632,18 +1656,36 @@
 6. 检查是否碰撞</t>
         </is>
       </c>
-      <c r="Q5" s="21" t="inlineStr"/>
-      <c r="R5" s="21" t="inlineStr"/>
-      <c r="S5" s="21" t="inlineStr"/>
-      <c r="T5" s="21" t="inlineStr"/>
-      <c r="U5" s="21" t="inlineStr">
+      <c r="Q5" s="20" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R5" s="20" t="inlineStr"/>
+      <c r="S5" s="20" t="inlineStr"/>
+      <c r="T5" s="20" t="inlineStr"/>
+      <c r="U5" s="20" t="inlineStr">
         <is>
           <t>基准用例,必须全部Pass才能继续偏移测试</t>
         </is>
       </c>
+      <c r="V5" s="28" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="W5" s="28" t="inlineStr"/>
+      <c r="X5" s="28" t="inlineStr"/>
+      <c r="Y5" s="28" t="inlineStr"/>
+      <c r="Z5" s="28" t="inlineStr"/>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-06 01:30:51</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>TC-OFF-003</t>
         </is>
@@ -1653,74 +1695,74 @@
           <t>S3</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>中货架B</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>0.85×0.8m</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>无偏移(基准)</t>
         </is>
       </c>
-      <c r="F6" s="21" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>货架位置与地图完全一致,无偏移</t>
         </is>
       </c>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H6" s="21" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="I6" s="21" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="J6" s="23" t="inlineStr">
+      <c r="J6" s="22" t="inlineStr">
         <is>
           <t>基准</t>
         </is>
       </c>
-      <c r="K6" s="21" t="inlineStr">
+      <c r="K6" s="20" t="inlineStr">
         <is>
           <t>导航至货架位置,停靠精度±5cm内</t>
         </is>
       </c>
-      <c r="L6" s="21" t="inlineStr">
+      <c r="L6" s="20" t="inlineStr">
         <is>
           <t>路径规划正常,无异常绕行</t>
         </is>
       </c>
-      <c r="M6" s="21" t="inlineStr">
+      <c r="M6" s="20" t="inlineStr">
         <is>
           <t>到达货架后，ROS自动修正匹配路径，稳定后退进入货架下，不会触发避障调整</t>
         </is>
       </c>
-      <c r="N6" s="21" t="inlineStr">
+      <c r="N6" s="20" t="inlineStr">
         <is>
           <t>匹配成功:机器人到达货架位置并完成停靠</t>
         </is>
       </c>
-      <c r="O6" s="21" t="inlineStr">
+      <c r="O6" s="20" t="inlineStr">
         <is>
           <t>1. 中货架B(0.85×0.8m)摆放至地图标记位置
 2. APP下发标准货架尺寸配置
 3. 机器人已建图并定位</t>
         </is>
       </c>
-      <c r="P6" s="21" t="inlineStr">
+      <c r="P6" s="20" t="inlineStr">
         <is>
           <t>1. APP下发导航任务至中货架B位置
 2. 机器人导航至目标点
@@ -1730,18 +1772,36 @@
 6. 检查是否碰撞</t>
         </is>
       </c>
-      <c r="Q6" s="21" t="inlineStr"/>
-      <c r="R6" s="21" t="inlineStr"/>
-      <c r="S6" s="21" t="inlineStr"/>
-      <c r="T6" s="21" t="inlineStr"/>
-      <c r="U6" s="21" t="inlineStr">
+      <c r="Q6" s="20" t="inlineStr"/>
+      <c r="R6" s="20" t="inlineStr"/>
+      <c r="S6" s="20" t="inlineStr"/>
+      <c r="T6" s="20" t="inlineStr"/>
+      <c r="U6" s="20" t="inlineStr">
         <is>
           <t>基准用例,必须全部Pass才能继续偏移测试</t>
         </is>
       </c>
+      <c r="V6" s="28" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="W6" s="28" t="n"/>
+      <c r="X6" s="28" t="n"/>
+      <c r="Y6" s="28" t="n"/>
+      <c r="Z6" s="28" t="inlineStr">
+        <is>
+          <t>2026-07-06 01:10:01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-06 01:10:02</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>TC-OFF-004</t>
         </is>
@@ -1751,74 +1811,74 @@
           <t>S4</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>窄货架</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>1.2×0.5m</t>
         </is>
       </c>
-      <c r="E7" s="21" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>无偏移(基准)</t>
         </is>
       </c>
-      <c r="F7" s="21" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>货架位置与地图完全一致,无偏移</t>
         </is>
       </c>
-      <c r="G7" s="21" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H7" s="21" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I7" s="22" t="inlineStr">
+      <c r="I7" s="21" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="J7" s="23" t="inlineStr">
+      <c r="J7" s="22" t="inlineStr">
         <is>
           <t>基准</t>
         </is>
       </c>
-      <c r="K7" s="21" t="inlineStr">
+      <c r="K7" s="20" t="inlineStr">
         <is>
           <t>导航至货架位置,停靠精度±5cm内</t>
         </is>
       </c>
-      <c r="L7" s="21" t="inlineStr">
+      <c r="L7" s="20" t="inlineStr">
         <is>
           <t>路径规划正常,无异常绕行</t>
         </is>
       </c>
-      <c r="M7" s="21" t="inlineStr">
+      <c r="M7" s="20" t="inlineStr">
         <is>
           <t>到达货架后，ROS自动修正匹配路径，稳定后退进入货架下，不会触发避障调整</t>
         </is>
       </c>
-      <c r="N7" s="21" t="inlineStr">
+      <c r="N7" s="20" t="inlineStr">
         <is>
           <t>匹配成功:机器人到达货架位置并完成停靠</t>
         </is>
       </c>
-      <c r="O7" s="21" t="inlineStr">
+      <c r="O7" s="20" t="inlineStr">
         <is>
           <t>1. 窄货架(1.2×0.5m)摆放至地图标记位置
 2. APP下发标准货架尺寸配置
 3. 机器人已建图并定位</t>
         </is>
       </c>
-      <c r="P7" s="21" t="inlineStr">
+      <c r="P7" s="20" t="inlineStr">
         <is>
           <t>1. APP下发导航任务至窄货架位置
 2. 机器人导航至目标点
@@ -1828,18 +1888,36 @@
 6. 检查是否碰撞</t>
         </is>
       </c>
-      <c r="Q7" s="21" t="inlineStr"/>
-      <c r="R7" s="21" t="inlineStr"/>
-      <c r="S7" s="21" t="inlineStr"/>
-      <c r="T7" s="21" t="inlineStr"/>
-      <c r="U7" s="21" t="inlineStr">
+      <c r="Q7" s="20" t="inlineStr"/>
+      <c r="R7" s="20" t="inlineStr"/>
+      <c r="S7" s="20" t="inlineStr"/>
+      <c r="T7" s="20" t="inlineStr"/>
+      <c r="U7" s="20" t="inlineStr">
         <is>
           <t>基准用例,必须全部Pass才能继续偏移测试</t>
         </is>
       </c>
+      <c r="V7" s="28" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="W7" s="28" t="n"/>
+      <c r="X7" s="28" t="n"/>
+      <c r="Y7" s="28" t="n"/>
+      <c r="Z7" s="28" t="inlineStr">
+        <is>
+          <t>2026-07-06 01:10:13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-06 01:10:14</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="21" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>TC-OFF-005</t>
         </is>
@@ -1849,74 +1927,74 @@
           <t>S5</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>大方货架</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>1.1×1.1m</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>无偏移(基准)</t>
         </is>
       </c>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>货架位置与地图完全一致,无偏移</t>
         </is>
       </c>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H8" s="21" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I8" s="22" t="inlineStr">
+      <c r="I8" s="21" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="J8" s="23" t="inlineStr">
+      <c r="J8" s="22" t="inlineStr">
         <is>
           <t>基准</t>
         </is>
       </c>
-      <c r="K8" s="21" t="inlineStr">
+      <c r="K8" s="20" t="inlineStr">
         <is>
           <t>导航至货架位置,停靠精度±5cm内</t>
         </is>
       </c>
-      <c r="L8" s="21" t="inlineStr">
+      <c r="L8" s="20" t="inlineStr">
         <is>
           <t>路径规划正常,无异常绕行</t>
         </is>
       </c>
-      <c r="M8" s="21" t="inlineStr">
+      <c r="M8" s="20" t="inlineStr">
         <is>
           <t>到达货架后，ROS自动修正匹配路径，稳定后退进入货架下，不会触发避障调整</t>
         </is>
       </c>
-      <c r="N8" s="21" t="inlineStr">
+      <c r="N8" s="20" t="inlineStr">
         <is>
           <t>匹配成功:机器人到达货架位置并完成停靠</t>
         </is>
       </c>
-      <c r="O8" s="21" t="inlineStr">
+      <c r="O8" s="20" t="inlineStr">
         <is>
           <t>1. 大方货架(1.1×1.1m)摆放至地图标记位置
 2. APP下发标准货架尺寸配置
 3. 机器人已建图并定位</t>
         </is>
       </c>
-      <c r="P8" s="21" t="inlineStr">
+      <c r="P8" s="20" t="inlineStr">
         <is>
           <t>1. APP下发导航任务至大方货架位置
 2. 机器人导航至目标点
@@ -1926,18 +2004,23 @@
 6. 检查是否碰撞</t>
         </is>
       </c>
-      <c r="Q8" s="21" t="inlineStr"/>
-      <c r="R8" s="21" t="inlineStr"/>
-      <c r="S8" s="21" t="inlineStr"/>
-      <c r="T8" s="21" t="inlineStr"/>
-      <c r="U8" s="21" t="inlineStr">
+      <c r="Q8" s="20" t="inlineStr"/>
+      <c r="R8" s="20" t="inlineStr"/>
+      <c r="S8" s="20" t="inlineStr"/>
+      <c r="T8" s="20" t="inlineStr"/>
+      <c r="U8" s="20" t="inlineStr">
         <is>
           <t>基准用例,必须全部Pass才能继续偏移测试</t>
         </is>
       </c>
+      <c r="V8" s="28" t="n"/>
+      <c r="W8" s="28" t="n"/>
+      <c r="X8" s="28" t="n"/>
+      <c r="Y8" s="28" t="n"/>
+      <c r="Z8" s="28" t="n"/>
     </row>
     <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="21" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>TC-OFF-006</t>
         </is>
@@ -1947,74 +2030,74 @@
           <t>S6</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>大长货架A</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>1.2×1m</t>
         </is>
       </c>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>无偏移(基准)</t>
         </is>
       </c>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>货架位置与地图完全一致,无偏移</t>
         </is>
       </c>
-      <c r="G9" s="21" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H9" s="21" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="I9" s="21" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="J9" s="23" t="inlineStr">
+      <c r="J9" s="22" t="inlineStr">
         <is>
           <t>基准</t>
         </is>
       </c>
-      <c r="K9" s="21" t="inlineStr">
+      <c r="K9" s="20" t="inlineStr">
         <is>
           <t>导航至货架位置,停靠精度±5cm内</t>
         </is>
       </c>
-      <c r="L9" s="21" t="inlineStr">
+      <c r="L9" s="20" t="inlineStr">
         <is>
           <t>路径规划正常,无异常绕行</t>
         </is>
       </c>
-      <c r="M9" s="21" t="inlineStr">
+      <c r="M9" s="20" t="inlineStr">
         <is>
           <t>到达货架后，ROS自动修正匹配路径，稳定后退进入货架下，不会触发避障调整</t>
         </is>
       </c>
-      <c r="N9" s="21" t="inlineStr">
+      <c r="N9" s="20" t="inlineStr">
         <is>
           <t>匹配成功:机器人到达货架位置并完成停靠</t>
         </is>
       </c>
-      <c r="O9" s="21" t="inlineStr">
+      <c r="O9" s="20" t="inlineStr">
         <is>
           <t>1. 大长货架A(1.2×1m)摆放至地图标记位置
 2. APP下发标准货架尺寸配置
 3. 机器人已建图并定位</t>
         </is>
       </c>
-      <c r="P9" s="21" t="inlineStr">
+      <c r="P9" s="20" t="inlineStr">
         <is>
           <t>1. APP下发导航任务至大长货架A位置
 2. 机器人导航至目标点
@@ -2024,18 +2107,32 @@
 6. 检查是否碰撞</t>
         </is>
       </c>
-      <c r="Q9" s="21" t="inlineStr"/>
-      <c r="R9" s="21" t="inlineStr"/>
-      <c r="S9" s="21" t="inlineStr"/>
-      <c r="T9" s="21" t="inlineStr"/>
-      <c r="U9" s="21" t="inlineStr">
+      <c r="Q9" s="20" t="inlineStr"/>
+      <c r="R9" s="20" t="inlineStr"/>
+      <c r="S9" s="20" t="inlineStr"/>
+      <c r="T9" s="20" t="inlineStr"/>
+      <c r="U9" s="20" t="inlineStr">
         <is>
           <t>基准用例,必须全部Pass才能继续偏移测试</t>
         </is>
       </c>
+      <c r="V9" s="28" t="inlineStr">
+        <is>
+          <t>阻塞</t>
+        </is>
+      </c>
+      <c r="W9" s="28" t="inlineStr"/>
+      <c r="X9" s="28" t="inlineStr"/>
+      <c r="Y9" s="28" t="inlineStr"/>
+      <c r="Z9" s="28" t="inlineStr"/>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-06 01:31:07</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="21" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>TC-OFF-007</t>
         </is>
@@ -2045,74 +2142,74 @@
           <t>S7</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>大长货架B</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>1×1.2m</t>
         </is>
       </c>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>无偏移(基准)</t>
         </is>
       </c>
-      <c r="F10" s="21" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>货架位置与地图完全一致,无偏移</t>
         </is>
       </c>
-      <c r="G10" s="21" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H10" s="21" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I10" s="22" t="inlineStr">
+      <c r="I10" s="21" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="J10" s="23" t="inlineStr">
+      <c r="J10" s="22" t="inlineStr">
         <is>
           <t>基准</t>
         </is>
       </c>
-      <c r="K10" s="21" t="inlineStr">
+      <c r="K10" s="20" t="inlineStr">
         <is>
           <t>导航至货架位置,停靠精度±5cm内</t>
         </is>
       </c>
-      <c r="L10" s="21" t="inlineStr">
+      <c r="L10" s="20" t="inlineStr">
         <is>
           <t>路径规划正常,无异常绕行</t>
         </is>
       </c>
-      <c r="M10" s="21" t="inlineStr">
+      <c r="M10" s="20" t="inlineStr">
         <is>
           <t>到达货架后，ROS自动修正匹配路径，稳定后退进入货架下，不会触发避障调整</t>
         </is>
       </c>
-      <c r="N10" s="21" t="inlineStr">
+      <c r="N10" s="20" t="inlineStr">
         <is>
           <t>匹配成功:机器人到达货架位置并完成停靠</t>
         </is>
       </c>
-      <c r="O10" s="21" t="inlineStr">
+      <c r="O10" s="20" t="inlineStr">
         <is>
           <t>1. 大长货架B(1×1.2m)摆放至地图标记位置
 2. APP下发标准货架尺寸配置
 3. 机器人已建图并定位</t>
         </is>
       </c>
-      <c r="P10" s="21" t="inlineStr">
+      <c r="P10" s="20" t="inlineStr">
         <is>
           <t>1. APP下发导航任务至大长货架B位置
 2. 机器人导航至目标点
@@ -2122,18 +2219,23 @@
 6. 检查是否碰撞</t>
         </is>
       </c>
-      <c r="Q10" s="21" t="inlineStr"/>
-      <c r="R10" s="21" t="inlineStr"/>
-      <c r="S10" s="21" t="inlineStr"/>
-      <c r="T10" s="21" t="inlineStr"/>
-      <c r="U10" s="21" t="inlineStr">
+      <c r="Q10" s="20" t="inlineStr"/>
+      <c r="R10" s="20" t="inlineStr"/>
+      <c r="S10" s="20" t="inlineStr"/>
+      <c r="T10" s="20" t="inlineStr"/>
+      <c r="U10" s="20" t="inlineStr">
         <is>
           <t>基准用例,必须全部Pass才能继续偏移测试</t>
         </is>
       </c>
+      <c r="V10" s="28" t="n"/>
+      <c r="W10" s="28" t="n"/>
+      <c r="X10" s="28" t="n"/>
+      <c r="Y10" s="28" t="n"/>
+      <c r="Z10" s="28" t="n"/>
     </row>
     <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="21" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>TC-OFF-008</t>
         </is>
@@ -2143,74 +2245,74 @@
           <t>S8</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>小货架(对齐尾部)</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>0.76×0.5m</t>
         </is>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>无偏移(基准)</t>
         </is>
       </c>
-      <c r="F11" s="21" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>货架位置与地图完全一致,无偏移</t>
         </is>
       </c>
-      <c r="G11" s="21" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H11" s="21" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I11" s="22" t="inlineStr">
+      <c r="I11" s="21" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="J11" s="23" t="inlineStr">
+      <c r="J11" s="22" t="inlineStr">
         <is>
           <t>基准</t>
         </is>
       </c>
-      <c r="K11" s="21" t="inlineStr">
+      <c r="K11" s="20" t="inlineStr">
         <is>
           <t>导航至货架位置,停靠精度±5cm内</t>
         </is>
       </c>
-      <c r="L11" s="21" t="inlineStr">
+      <c r="L11" s="20" t="inlineStr">
         <is>
           <t>路径规划正常,无异常绕行</t>
         </is>
       </c>
-      <c r="M11" s="21" t="inlineStr">
+      <c r="M11" s="20" t="inlineStr">
         <is>
           <t>到达货架后，ROS自动修正匹配路径，稳定后退进入货架下，不会触发避障调整</t>
         </is>
       </c>
-      <c r="N11" s="21" t="inlineStr">
+      <c r="N11" s="20" t="inlineStr">
         <is>
           <t>匹配成功:机器人到达货架位置并完成停靠</t>
         </is>
       </c>
-      <c r="O11" s="21" t="inlineStr">
+      <c r="O11" s="20" t="inlineStr">
         <is>
           <t>1. 小货架(对齐尾部)(0.76×0.5m)摆放至地图标记位置
 2. APP下发标准货架尺寸配置（调整后退距离，货架对齐尾部）
 3. 机器人已建图并定位</t>
         </is>
       </c>
-      <c r="P11" s="21" t="inlineStr">
+      <c r="P11" s="20" t="inlineStr">
         <is>
           <t>1. APP下发导航任务至小货架(对齐尾部)位置
 2. 机器人导航至目标点
@@ -2220,18 +2322,23 @@
 6. 检查是否碰撞</t>
         </is>
       </c>
-      <c r="Q11" s="21" t="inlineStr"/>
-      <c r="R11" s="21" t="inlineStr"/>
-      <c r="S11" s="21" t="inlineStr"/>
-      <c r="T11" s="21" t="inlineStr"/>
-      <c r="U11" s="21" t="inlineStr">
+      <c r="Q11" s="20" t="inlineStr"/>
+      <c r="R11" s="20" t="inlineStr"/>
+      <c r="S11" s="20" t="inlineStr"/>
+      <c r="T11" s="20" t="inlineStr"/>
+      <c r="U11" s="20" t="inlineStr">
         <is>
           <t>基准用例,必须全部Pass才能继续偏移测试</t>
         </is>
       </c>
+      <c r="V11" s="28" t="n"/>
+      <c r="W11" s="28" t="n"/>
+      <c r="X11" s="28" t="n"/>
+      <c r="Y11" s="28" t="n"/>
+      <c r="Z11" s="28" t="n"/>
     </row>
     <row r="12" ht="60" customHeight="1">
-      <c r="A12" s="21" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>TC-OFF-009</t>
         </is>
@@ -2241,74 +2348,74 @@
           <t>S9</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>窄货架(对齐尾部)</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>1.2×0.5m</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>无偏移(基准)</t>
         </is>
       </c>
-      <c r="F12" s="21" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>货架位置与地图完全一致,无偏移</t>
         </is>
       </c>
-      <c r="G12" s="21" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H12" s="21" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="I12" s="21" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="J12" s="23" t="inlineStr">
+      <c r="J12" s="22" t="inlineStr">
         <is>
           <t>基准</t>
         </is>
       </c>
-      <c r="K12" s="21" t="inlineStr">
+      <c r="K12" s="20" t="inlineStr">
         <is>
           <t>导航至货架位置,停靠精度±5cm内</t>
         </is>
       </c>
-      <c r="L12" s="21" t="inlineStr">
+      <c r="L12" s="20" t="inlineStr">
         <is>
           <t>路径规划正常,无异常绕行</t>
         </is>
       </c>
-      <c r="M12" s="21" t="inlineStr">
+      <c r="M12" s="20" t="inlineStr">
         <is>
           <t>到达货架后，ROS自动修正匹配路径，稳定后退进入货架下，不会触发避障调整</t>
         </is>
       </c>
-      <c r="N12" s="21" t="inlineStr">
+      <c r="N12" s="20" t="inlineStr">
         <is>
           <t>匹配成功:机器人到达货架位置并完成停靠</t>
         </is>
       </c>
-      <c r="O12" s="21" t="inlineStr">
+      <c r="O12" s="20" t="inlineStr">
         <is>
           <t>1. 窄货架(对齐尾部)(1.2×0.5m)摆放至地图标记位置
 2. APP下发标准货架尺寸配置（调整后退距离，货架对齐尾部）
 3. 机器人已建图并定位</t>
         </is>
       </c>
-      <c r="P12" s="21" t="inlineStr">
+      <c r="P12" s="20" t="inlineStr">
         <is>
           <t>1. APP下发导航任务至窄货架(对齐尾部)位置
 2. 机器人导航至目标点
@@ -2318,15 +2425,20 @@
 6. 检查是否碰撞</t>
         </is>
       </c>
-      <c r="Q12" s="21" t="inlineStr"/>
-      <c r="R12" s="21" t="inlineStr"/>
-      <c r="S12" s="21" t="inlineStr"/>
-      <c r="T12" s="21" t="inlineStr"/>
-      <c r="U12" s="21" t="inlineStr">
+      <c r="Q12" s="20" t="inlineStr"/>
+      <c r="R12" s="20" t="inlineStr"/>
+      <c r="S12" s="20" t="inlineStr"/>
+      <c r="T12" s="20" t="inlineStr"/>
+      <c r="U12" s="20" t="inlineStr">
         <is>
           <t>基准用例,必须全部Pass才能继续偏移测试</t>
         </is>
       </c>
+      <c r="V12" s="28" t="n"/>
+      <c r="W12" s="28" t="n"/>
+      <c r="X12" s="28" t="n"/>
+      <c r="Y12" s="28" t="n"/>
+      <c r="Z12" s="20" t="inlineStr"/>
     </row>
     <row r="13" ht="60" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
@@ -2369,12 +2481,12 @@
           <t>10cm</t>
         </is>
       </c>
-      <c r="I13" s="24" t="inlineStr">
+      <c r="I13" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J13" s="25" t="inlineStr">
+      <c r="J13" s="24" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -2432,6 +2544,11 @@
           <t>偏移方向:前偏10cm, 风险等级:高</t>
         </is>
       </c>
+      <c r="V13" s="28" t="n"/>
+      <c r="W13" s="28" t="n"/>
+      <c r="X13" s="28" t="n"/>
+      <c r="Y13" s="28" t="n"/>
+      <c r="Z13" s="28" t="n"/>
     </row>
     <row r="14" ht="60" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
@@ -2444,8 +2561,8 @@
           <t>S1</t>
         </is>
       </c>
-      <c r="C14" s="29" t="n"/>
-      <c r="D14" s="29" t="n"/>
+      <c r="C14" s="11" t="n"/>
+      <c r="D14" s="11" t="n"/>
       <c r="E14" s="4" t="inlineStr">
         <is>
           <t>后偏10cm</t>
@@ -2466,12 +2583,12 @@
           <t>10cm</t>
         </is>
       </c>
-      <c r="I14" s="24" t="inlineStr">
+      <c r="I14" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J14" s="25" t="inlineStr">
+      <c r="J14" s="24" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -2529,6 +2646,11 @@
           <t>偏移方向:后偏10cm, 风险等级:高</t>
         </is>
       </c>
+      <c r="V14" s="28" t="n"/>
+      <c r="W14" s="28" t="n"/>
+      <c r="X14" s="28" t="n"/>
+      <c r="Y14" s="28" t="n"/>
+      <c r="Z14" s="28" t="n"/>
     </row>
     <row r="15" ht="60" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -2541,8 +2663,8 @@
           <t>S1</t>
         </is>
       </c>
-      <c r="C15" s="29" t="n"/>
-      <c r="D15" s="29" t="n"/>
+      <c r="C15" s="11" t="n"/>
+      <c r="D15" s="11" t="n"/>
       <c r="E15" s="4" t="inlineStr">
         <is>
           <t>左偏10cm</t>
@@ -2563,12 +2685,12 @@
           <t>10cm</t>
         </is>
       </c>
-      <c r="I15" s="24" t="inlineStr">
+      <c r="I15" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J15" s="25" t="inlineStr">
+      <c r="J15" s="24" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -2626,6 +2748,11 @@
           <t>偏移方向:左偏10cm, 风险等级:高</t>
         </is>
       </c>
+      <c r="V15" s="28" t="n"/>
+      <c r="W15" s="28" t="n"/>
+      <c r="X15" s="28" t="n"/>
+      <c r="Y15" s="28" t="n"/>
+      <c r="Z15" s="28" t="n"/>
     </row>
     <row r="16" ht="60" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
@@ -2638,8 +2765,8 @@
           <t>S1</t>
         </is>
       </c>
-      <c r="C16" s="29" t="n"/>
-      <c r="D16" s="29" t="n"/>
+      <c r="C16" s="11" t="n"/>
+      <c r="D16" s="11" t="n"/>
       <c r="E16" s="4" t="inlineStr">
         <is>
           <t>右偏10cm</t>
@@ -2660,12 +2787,12 @@
           <t>10cm</t>
         </is>
       </c>
-      <c r="I16" s="24" t="inlineStr">
+      <c r="I16" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J16" s="25" t="inlineStr">
+      <c r="J16" s="24" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -2723,6 +2850,11 @@
           <t>偏移方向:右偏10cm, 风险等级:高</t>
         </is>
       </c>
+      <c r="V16" s="28" t="n"/>
+      <c r="W16" s="28" t="n"/>
+      <c r="X16" s="28" t="n"/>
+      <c r="Y16" s="28" t="n"/>
+      <c r="Z16" s="28" t="n"/>
     </row>
     <row r="17" ht="60" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
@@ -2735,8 +2867,8 @@
           <t>S1</t>
         </is>
       </c>
-      <c r="C17" s="29" t="n"/>
-      <c r="D17" s="29" t="n"/>
+      <c r="C17" s="11" t="n"/>
+      <c r="D17" s="11" t="n"/>
       <c r="E17" s="4" t="inlineStr">
         <is>
           <t>左偏3°</t>
@@ -2757,12 +2889,12 @@
           <t>3°</t>
         </is>
       </c>
-      <c r="I17" s="24" t="inlineStr">
+      <c r="I17" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J17" s="26" t="inlineStr">
+      <c r="J17" s="25" t="inlineStr">
         <is>
           <t>低</t>
         </is>
@@ -2820,6 +2952,11 @@
           <t>偏移方向:左偏3°, 风险等级:低</t>
         </is>
       </c>
+      <c r="V17" s="28" t="n"/>
+      <c r="W17" s="28" t="n"/>
+      <c r="X17" s="28" t="n"/>
+      <c r="Y17" s="28" t="n"/>
+      <c r="Z17" s="28" t="n"/>
     </row>
     <row r="18" ht="60" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
@@ -2832,8 +2969,8 @@
           <t>S1</t>
         </is>
       </c>
-      <c r="C18" s="30" t="n"/>
-      <c r="D18" s="30" t="n"/>
+      <c r="C18" s="12" t="n"/>
+      <c r="D18" s="12" t="n"/>
       <c r="E18" s="4" t="inlineStr">
         <is>
           <t>右偏3°</t>
@@ -2854,12 +2991,12 @@
           <t>3°</t>
         </is>
       </c>
-      <c r="I18" s="24" t="inlineStr">
+      <c r="I18" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J18" s="26" t="inlineStr">
+      <c r="J18" s="25" t="inlineStr">
         <is>
           <t>低</t>
         </is>
@@ -2917,6 +3054,11 @@
           <t>偏移方向:右偏3°, 风险等级:低</t>
         </is>
       </c>
+      <c r="V18" s="28" t="n"/>
+      <c r="W18" s="28" t="n"/>
+      <c r="X18" s="28" t="n"/>
+      <c r="Y18" s="28" t="n"/>
+      <c r="Z18" s="28" t="n"/>
     </row>
     <row r="19" ht="60" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
@@ -2959,12 +3101,12 @@
           <t>10cm</t>
         </is>
       </c>
-      <c r="I19" s="24" t="inlineStr">
+      <c r="I19" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J19" s="27" t="inlineStr">
+      <c r="J19" s="26" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -3022,6 +3164,11 @@
           <t>偏移方向:前偏10cm, 风险等级:中</t>
         </is>
       </c>
+      <c r="V19" s="28" t="n"/>
+      <c r="W19" s="28" t="n"/>
+      <c r="X19" s="28" t="n"/>
+      <c r="Y19" s="28" t="n"/>
+      <c r="Z19" s="28" t="n"/>
     </row>
     <row r="20" ht="60" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
@@ -3034,8 +3181,8 @@
           <t>S2</t>
         </is>
       </c>
-      <c r="C20" s="29" t="n"/>
-      <c r="D20" s="29" t="n"/>
+      <c r="C20" s="11" t="n"/>
+      <c r="D20" s="11" t="n"/>
       <c r="E20" s="4" t="inlineStr">
         <is>
           <t>后偏10cm</t>
@@ -3056,12 +3203,12 @@
           <t>10cm</t>
         </is>
       </c>
-      <c r="I20" s="24" t="inlineStr">
+      <c r="I20" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J20" s="27" t="inlineStr">
+      <c r="J20" s="26" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -3119,6 +3266,11 @@
           <t>偏移方向:后偏10cm, 风险等级:中</t>
         </is>
       </c>
+      <c r="V20" s="28" t="n"/>
+      <c r="W20" s="28" t="n"/>
+      <c r="X20" s="28" t="n"/>
+      <c r="Y20" s="28" t="n"/>
+      <c r="Z20" s="28" t="n"/>
     </row>
     <row r="21" ht="60" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
@@ -3131,8 +3283,8 @@
           <t>S2</t>
         </is>
       </c>
-      <c r="C21" s="29" t="n"/>
-      <c r="D21" s="29" t="n"/>
+      <c r="C21" s="11" t="n"/>
+      <c r="D21" s="11" t="n"/>
       <c r="E21" s="4" t="inlineStr">
         <is>
           <t>左偏10cm</t>
@@ -3153,12 +3305,12 @@
           <t>10cm</t>
         </is>
       </c>
-      <c r="I21" s="24" t="inlineStr">
+      <c r="I21" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J21" s="27" t="inlineStr">
+      <c r="J21" s="26" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -3216,6 +3368,11 @@
           <t>偏移方向:左偏10cm, 风险等级:中</t>
         </is>
       </c>
+      <c r="V21" s="28" t="n"/>
+      <c r="W21" s="28" t="n"/>
+      <c r="X21" s="28" t="n"/>
+      <c r="Y21" s="28" t="n"/>
+      <c r="Z21" s="28" t="n"/>
     </row>
     <row r="22" ht="60" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
@@ -3228,8 +3385,8 @@
           <t>S2</t>
         </is>
       </c>
-      <c r="C22" s="29" t="n"/>
-      <c r="D22" s="29" t="n"/>
+      <c r="C22" s="11" t="n"/>
+      <c r="D22" s="11" t="n"/>
       <c r="E22" s="4" t="inlineStr">
         <is>
           <t>右偏10cm</t>
@@ -3250,12 +3407,12 @@
           <t>10cm</t>
         </is>
       </c>
-      <c r="I22" s="24" t="inlineStr">
+      <c r="I22" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J22" s="27" t="inlineStr">
+      <c r="J22" s="26" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -3313,6 +3470,11 @@
           <t>偏移方向:右偏10cm, 风险等级:中</t>
         </is>
       </c>
+      <c r="V22" s="28" t="n"/>
+      <c r="W22" s="28" t="n"/>
+      <c r="X22" s="28" t="n"/>
+      <c r="Y22" s="28" t="n"/>
+      <c r="Z22" s="28" t="n"/>
     </row>
     <row r="23" ht="60" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
@@ -3325,8 +3487,8 @@
           <t>S2</t>
         </is>
       </c>
-      <c r="C23" s="29" t="n"/>
-      <c r="D23" s="29" t="n"/>
+      <c r="C23" s="11" t="n"/>
+      <c r="D23" s="11" t="n"/>
       <c r="E23" s="4" t="inlineStr">
         <is>
           <t>左偏3°</t>
@@ -3347,12 +3509,12 @@
           <t>3°</t>
         </is>
       </c>
-      <c r="I23" s="24" t="inlineStr">
+      <c r="I23" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J23" s="26" t="inlineStr">
+      <c r="J23" s="25" t="inlineStr">
         <is>
           <t>低</t>
         </is>
@@ -3410,6 +3572,11 @@
           <t>偏移方向:左偏3°, 风险等级:低</t>
         </is>
       </c>
+      <c r="V23" s="28" t="n"/>
+      <c r="W23" s="28" t="n"/>
+      <c r="X23" s="28" t="n"/>
+      <c r="Y23" s="28" t="n"/>
+      <c r="Z23" s="28" t="n"/>
     </row>
     <row r="24" ht="60" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
@@ -3422,8 +3589,8 @@
           <t>S2</t>
         </is>
       </c>
-      <c r="C24" s="30" t="n"/>
-      <c r="D24" s="30" t="n"/>
+      <c r="C24" s="12" t="n"/>
+      <c r="D24" s="12" t="n"/>
       <c r="E24" s="4" t="inlineStr">
         <is>
           <t>右偏3°</t>
@@ -3444,12 +3611,12 @@
           <t>3°</t>
         </is>
       </c>
-      <c r="I24" s="24" t="inlineStr">
+      <c r="I24" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J24" s="26" t="inlineStr">
+      <c r="J24" s="25" t="inlineStr">
         <is>
           <t>低</t>
         </is>
@@ -3507,6 +3674,11 @@
           <t>偏移方向:右偏3°, 风险等级:低</t>
         </is>
       </c>
+      <c r="V24" s="28" t="n"/>
+      <c r="W24" s="28" t="n"/>
+      <c r="X24" s="28" t="n"/>
+      <c r="Y24" s="28" t="n"/>
+      <c r="Z24" s="28" t="n"/>
     </row>
     <row r="25" ht="60" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
@@ -3549,12 +3721,12 @@
           <t>10cm</t>
         </is>
       </c>
-      <c r="I25" s="24" t="inlineStr">
+      <c r="I25" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J25" s="27" t="inlineStr">
+      <c r="J25" s="26" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -3612,6 +3784,11 @@
           <t>偏移方向:前偏10cm, 风险等级:中</t>
         </is>
       </c>
+      <c r="V25" s="28" t="n"/>
+      <c r="W25" s="28" t="n"/>
+      <c r="X25" s="28" t="n"/>
+      <c r="Y25" s="28" t="n"/>
+      <c r="Z25" s="28" t="n"/>
     </row>
     <row r="26" ht="60" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
@@ -3624,8 +3801,8 @@
           <t>S3</t>
         </is>
       </c>
-      <c r="C26" s="29" t="n"/>
-      <c r="D26" s="29" t="n"/>
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="11" t="n"/>
       <c r="E26" s="4" t="inlineStr">
         <is>
           <t>后偏10cm</t>
@@ -3646,12 +3823,12 @@
           <t>10cm</t>
         </is>
       </c>
-      <c r="I26" s="24" t="inlineStr">
+      <c r="I26" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J26" s="27" t="inlineStr">
+      <c r="J26" s="26" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -3709,6 +3886,11 @@
           <t>偏移方向:后偏10cm, 风险等级:中</t>
         </is>
       </c>
+      <c r="V26" s="28" t="n"/>
+      <c r="W26" s="28" t="n"/>
+      <c r="X26" s="28" t="n"/>
+      <c r="Y26" s="28" t="n"/>
+      <c r="Z26" s="28" t="n"/>
     </row>
     <row r="27" ht="60" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
@@ -3721,8 +3903,8 @@
           <t>S3</t>
         </is>
       </c>
-      <c r="C27" s="29" t="n"/>
-      <c r="D27" s="29" t="n"/>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="11" t="n"/>
       <c r="E27" s="4" t="inlineStr">
         <is>
           <t>左偏10cm</t>
@@ -3743,12 +3925,12 @@
           <t>10cm</t>
         </is>
       </c>
-      <c r="I27" s="24" t="inlineStr">
+      <c r="I27" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J27" s="27" t="inlineStr">
+      <c r="J27" s="26" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -3806,6 +3988,11 @@
           <t>偏移方向:左偏10cm, 风险等级:中</t>
         </is>
       </c>
+      <c r="V27" s="28" t="n"/>
+      <c r="W27" s="28" t="n"/>
+      <c r="X27" s="28" t="n"/>
+      <c r="Y27" s="28" t="n"/>
+      <c r="Z27" s="28" t="n"/>
     </row>
     <row r="28" ht="60" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
@@ -3818,8 +4005,8 @@
           <t>S3</t>
         </is>
       </c>
-      <c r="C28" s="29" t="n"/>
-      <c r="D28" s="29" t="n"/>
+      <c r="C28" s="11" t="n"/>
+      <c r="D28" s="11" t="n"/>
       <c r="E28" s="4" t="inlineStr">
         <is>
           <t>右偏10cm</t>
@@ -3840,12 +4027,12 @@
           <t>10cm</t>
         </is>
       </c>
-      <c r="I28" s="24" t="inlineStr">
+      <c r="I28" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J28" s="27" t="inlineStr">
+      <c r="J28" s="26" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -3903,6 +4090,11 @@
           <t>偏移方向:右偏10cm, 风险等级:中</t>
         </is>
       </c>
+      <c r="V28" s="28" t="n"/>
+      <c r="W28" s="28" t="n"/>
+      <c r="X28" s="28" t="n"/>
+      <c r="Y28" s="28" t="n"/>
+      <c r="Z28" s="28" t="n"/>
     </row>
     <row r="29" ht="60" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
@@ -3915,8 +4107,8 @@
           <t>S3</t>
         </is>
       </c>
-      <c r="C29" s="29" t="n"/>
-      <c r="D29" s="29" t="n"/>
+      <c r="C29" s="11" t="n"/>
+      <c r="D29" s="11" t="n"/>
       <c r="E29" s="4" t="inlineStr">
         <is>
           <t>左偏3°</t>
@@ -3937,12 +4129,12 @@
           <t>3°</t>
         </is>
       </c>
-      <c r="I29" s="24" t="inlineStr">
+      <c r="I29" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J29" s="26" t="inlineStr">
+      <c r="J29" s="25" t="inlineStr">
         <is>
           <t>低</t>
         </is>
@@ -4000,6 +4192,11 @@
           <t>偏移方向:左偏3°, 风险等级:低</t>
         </is>
       </c>
+      <c r="V29" s="28" t="n"/>
+      <c r="W29" s="28" t="n"/>
+      <c r="X29" s="28" t="n"/>
+      <c r="Y29" s="28" t="n"/>
+      <c r="Z29" s="28" t="n"/>
     </row>
     <row r="30" ht="60" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
@@ -4012,8 +4209,8 @@
           <t>S3</t>
         </is>
       </c>
-      <c r="C30" s="30" t="n"/>
-      <c r="D30" s="30" t="n"/>
+      <c r="C30" s="12" t="n"/>
+      <c r="D30" s="12" t="n"/>
       <c r="E30" s="4" t="inlineStr">
         <is>
           <t>右偏3°</t>
@@ -4034,12 +4231,12 @@
           <t>3°</t>
         </is>
       </c>
-      <c r="I30" s="24" t="inlineStr">
+      <c r="I30" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J30" s="26" t="inlineStr">
+      <c r="J30" s="25" t="inlineStr">
         <is>
           <t>低</t>
         </is>
@@ -4097,6 +4294,11 @@
           <t>偏移方向:右偏3°, 风险等级:低</t>
         </is>
       </c>
+      <c r="V30" s="28" t="n"/>
+      <c r="W30" s="28" t="n"/>
+      <c r="X30" s="28" t="n"/>
+      <c r="Y30" s="28" t="n"/>
+      <c r="Z30" s="28" t="n"/>
     </row>
     <row r="31" ht="60" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
@@ -4139,12 +4341,12 @@
           <t>10cm</t>
         </is>
       </c>
-      <c r="I31" s="24" t="inlineStr">
+      <c r="I31" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J31" s="27" t="inlineStr">
+      <c r="J31" s="26" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -4202,6 +4404,11 @@
           <t>偏移方向:前偏10cm, 风险等级:中</t>
         </is>
       </c>
+      <c r="V31" s="28" t="n"/>
+      <c r="W31" s="28" t="n"/>
+      <c r="X31" s="28" t="n"/>
+      <c r="Y31" s="28" t="n"/>
+      <c r="Z31" s="28" t="n"/>
     </row>
     <row r="32" ht="60" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
@@ -4214,8 +4421,8 @@
           <t>S4</t>
         </is>
       </c>
-      <c r="C32" s="29" t="n"/>
-      <c r="D32" s="29" t="n"/>
+      <c r="C32" s="11" t="n"/>
+      <c r="D32" s="11" t="n"/>
       <c r="E32" s="4" t="inlineStr">
         <is>
           <t>后偏10cm</t>
@@ -4236,12 +4443,12 @@
           <t>10cm</t>
         </is>
       </c>
-      <c r="I32" s="24" t="inlineStr">
+      <c r="I32" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J32" s="27" t="inlineStr">
+      <c r="J32" s="26" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -4299,6 +4506,11 @@
           <t>偏移方向:后偏10cm, 风险等级:中</t>
         </is>
       </c>
+      <c r="V32" s="28" t="n"/>
+      <c r="W32" s="28" t="n"/>
+      <c r="X32" s="28" t="n"/>
+      <c r="Y32" s="28" t="n"/>
+      <c r="Z32" s="28" t="n"/>
     </row>
     <row r="33" ht="60" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
@@ -4311,8 +4523,8 @@
           <t>S4</t>
         </is>
       </c>
-      <c r="C33" s="29" t="n"/>
-      <c r="D33" s="29" t="n"/>
+      <c r="C33" s="11" t="n"/>
+      <c r="D33" s="11" t="n"/>
       <c r="E33" s="4" t="inlineStr">
         <is>
           <t>左偏10cm</t>
@@ -4333,12 +4545,12 @@
           <t>10cm</t>
         </is>
       </c>
-      <c r="I33" s="24" t="inlineStr">
+      <c r="I33" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J33" s="27" t="inlineStr">
+      <c r="J33" s="26" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -4396,6 +4608,11 @@
           <t>偏移方向:左偏10cm, 风险等级:中</t>
         </is>
       </c>
+      <c r="V33" s="28" t="n"/>
+      <c r="W33" s="28" t="n"/>
+      <c r="X33" s="28" t="n"/>
+      <c r="Y33" s="28" t="n"/>
+      <c r="Z33" s="28" t="n"/>
     </row>
     <row r="34" ht="60" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
@@ -4408,8 +4625,8 @@
           <t>S4</t>
         </is>
       </c>
-      <c r="C34" s="29" t="n"/>
-      <c r="D34" s="29" t="n"/>
+      <c r="C34" s="11" t="n"/>
+      <c r="D34" s="11" t="n"/>
       <c r="E34" s="4" t="inlineStr">
         <is>
           <t>右偏10cm</t>
@@ -4430,12 +4647,12 @@
           <t>10cm</t>
         </is>
       </c>
-      <c r="I34" s="24" t="inlineStr">
+      <c r="I34" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J34" s="27" t="inlineStr">
+      <c r="J34" s="26" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -4493,6 +4710,11 @@
           <t>偏移方向:右偏10cm, 风险等级:中</t>
         </is>
       </c>
+      <c r="V34" s="28" t="n"/>
+      <c r="W34" s="28" t="n"/>
+      <c r="X34" s="28" t="n"/>
+      <c r="Y34" s="28" t="n"/>
+      <c r="Z34" s="28" t="n"/>
     </row>
     <row r="35" ht="60" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
@@ -4505,8 +4727,8 @@
           <t>S4</t>
         </is>
       </c>
-      <c r="C35" s="29" t="n"/>
-      <c r="D35" s="29" t="n"/>
+      <c r="C35" s="11" t="n"/>
+      <c r="D35" s="11" t="n"/>
       <c r="E35" s="4" t="inlineStr">
         <is>
           <t>左偏3°</t>
@@ -4527,12 +4749,12 @@
           <t>3°</t>
         </is>
       </c>
-      <c r="I35" s="24" t="inlineStr">
+      <c r="I35" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J35" s="26" t="inlineStr">
+      <c r="J35" s="25" t="inlineStr">
         <is>
           <t>低</t>
         </is>
@@ -4590,6 +4812,11 @@
           <t>偏移方向:左偏3°, 风险等级:低</t>
         </is>
       </c>
+      <c r="V35" s="28" t="n"/>
+      <c r="W35" s="28" t="n"/>
+      <c r="X35" s="28" t="n"/>
+      <c r="Y35" s="28" t="n"/>
+      <c r="Z35" s="28" t="n"/>
     </row>
     <row r="36" ht="60" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
@@ -4602,8 +4829,8 @@
           <t>S4</t>
         </is>
       </c>
-      <c r="C36" s="30" t="n"/>
-      <c r="D36" s="30" t="n"/>
+      <c r="C36" s="12" t="n"/>
+      <c r="D36" s="12" t="n"/>
       <c r="E36" s="4" t="inlineStr">
         <is>
           <t>右偏3°</t>
@@ -4624,12 +4851,12 @@
           <t>3°</t>
         </is>
       </c>
-      <c r="I36" s="24" t="inlineStr">
+      <c r="I36" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J36" s="26" t="inlineStr">
+      <c r="J36" s="25" t="inlineStr">
         <is>
           <t>低</t>
         </is>
@@ -4687,6 +4914,11 @@
           <t>偏移方向:右偏3°, 风险等级:低</t>
         </is>
       </c>
+      <c r="V36" s="28" t="n"/>
+      <c r="W36" s="28" t="n"/>
+      <c r="X36" s="28" t="n"/>
+      <c r="Y36" s="28" t="n"/>
+      <c r="Z36" s="28" t="n"/>
     </row>
     <row r="37" ht="60" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
@@ -4729,12 +4961,12 @@
           <t>10cm</t>
         </is>
       </c>
-      <c r="I37" s="24" t="inlineStr">
+      <c r="I37" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J37" s="27" t="inlineStr">
+      <c r="J37" s="26" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -4792,6 +5024,11 @@
           <t>偏移方向:前偏10cm, 风险等级:中</t>
         </is>
       </c>
+      <c r="V37" s="28" t="n"/>
+      <c r="W37" s="28" t="n"/>
+      <c r="X37" s="28" t="n"/>
+      <c r="Y37" s="28" t="n"/>
+      <c r="Z37" s="28" t="n"/>
     </row>
     <row r="38" ht="60" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
@@ -4804,8 +5041,8 @@
           <t>S5</t>
         </is>
       </c>
-      <c r="C38" s="29" t="n"/>
-      <c r="D38" s="29" t="n"/>
+      <c r="C38" s="11" t="n"/>
+      <c r="D38" s="11" t="n"/>
       <c r="E38" s="4" t="inlineStr">
         <is>
           <t>后偏10cm</t>
@@ -4826,12 +5063,12 @@
           <t>10cm</t>
         </is>
       </c>
-      <c r="I38" s="24" t="inlineStr">
+      <c r="I38" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J38" s="27" t="inlineStr">
+      <c r="J38" s="26" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -4889,6 +5126,11 @@
           <t>偏移方向:后偏10cm, 风险等级:中</t>
         </is>
       </c>
+      <c r="V38" s="28" t="n"/>
+      <c r="W38" s="28" t="n"/>
+      <c r="X38" s="28" t="n"/>
+      <c r="Y38" s="28" t="n"/>
+      <c r="Z38" s="28" t="n"/>
     </row>
     <row r="39" ht="60" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
@@ -4901,8 +5143,8 @@
           <t>S5</t>
         </is>
       </c>
-      <c r="C39" s="29" t="n"/>
-      <c r="D39" s="29" t="n"/>
+      <c r="C39" s="11" t="n"/>
+      <c r="D39" s="11" t="n"/>
       <c r="E39" s="4" t="inlineStr">
         <is>
           <t>左偏10cm</t>
@@ -4923,12 +5165,12 @@
           <t>10cm</t>
         </is>
       </c>
-      <c r="I39" s="24" t="inlineStr">
+      <c r="I39" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J39" s="27" t="inlineStr">
+      <c r="J39" s="26" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -4986,6 +5228,11 @@
           <t>偏移方向:左偏10cm, 风险等级:中</t>
         </is>
       </c>
+      <c r="V39" s="28" t="n"/>
+      <c r="W39" s="28" t="n"/>
+      <c r="X39" s="28" t="n"/>
+      <c r="Y39" s="28" t="n"/>
+      <c r="Z39" s="28" t="n"/>
     </row>
     <row r="40" ht="60" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
@@ -4998,8 +5245,8 @@
           <t>S5</t>
         </is>
       </c>
-      <c r="C40" s="29" t="n"/>
-      <c r="D40" s="29" t="n"/>
+      <c r="C40" s="11" t="n"/>
+      <c r="D40" s="11" t="n"/>
       <c r="E40" s="4" t="inlineStr">
         <is>
           <t>右偏10cm</t>
@@ -5020,12 +5267,12 @@
           <t>10cm</t>
         </is>
       </c>
-      <c r="I40" s="24" t="inlineStr">
+      <c r="I40" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J40" s="27" t="inlineStr">
+      <c r="J40" s="26" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -5083,6 +5330,11 @@
           <t>偏移方向:右偏10cm, 风险等级:中</t>
         </is>
       </c>
+      <c r="V40" s="28" t="n"/>
+      <c r="W40" s="28" t="n"/>
+      <c r="X40" s="28" t="n"/>
+      <c r="Y40" s="28" t="n"/>
+      <c r="Z40" s="28" t="n"/>
     </row>
     <row r="41" ht="60" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
@@ -5095,8 +5347,8 @@
           <t>S5</t>
         </is>
       </c>
-      <c r="C41" s="29" t="n"/>
-      <c r="D41" s="29" t="n"/>
+      <c r="C41" s="11" t="n"/>
+      <c r="D41" s="11" t="n"/>
       <c r="E41" s="4" t="inlineStr">
         <is>
           <t>左偏3°</t>
@@ -5117,12 +5369,12 @@
           <t>3°</t>
         </is>
       </c>
-      <c r="I41" s="28" t="inlineStr">
+      <c r="I41" s="27" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="J41" s="26" t="inlineStr">
+      <c r="J41" s="25" t="inlineStr">
         <is>
           <t>低</t>
         </is>
@@ -5180,6 +5432,11 @@
           <t>偏移方向:左偏3°, 风险等级:低</t>
         </is>
       </c>
+      <c r="V41" s="28" t="n"/>
+      <c r="W41" s="28" t="n"/>
+      <c r="X41" s="28" t="n"/>
+      <c r="Y41" s="28" t="n"/>
+      <c r="Z41" s="28" t="n"/>
     </row>
     <row r="42" ht="60" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
@@ -5192,8 +5449,8 @@
           <t>S5</t>
         </is>
       </c>
-      <c r="C42" s="30" t="n"/>
-      <c r="D42" s="30" t="n"/>
+      <c r="C42" s="12" t="n"/>
+      <c r="D42" s="12" t="n"/>
       <c r="E42" s="4" t="inlineStr">
         <is>
           <t>右偏3°</t>
@@ -5214,12 +5471,12 @@
           <t>3°</t>
         </is>
       </c>
-      <c r="I42" s="28" t="inlineStr">
+      <c r="I42" s="27" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="J42" s="26" t="inlineStr">
+      <c r="J42" s="25" t="inlineStr">
         <is>
           <t>低</t>
         </is>
@@ -5277,6 +5534,11 @@
           <t>偏移方向:右偏3°, 风险等级:低</t>
         </is>
       </c>
+      <c r="V42" s="28" t="n"/>
+      <c r="W42" s="28" t="n"/>
+      <c r="X42" s="28" t="n"/>
+      <c r="Y42" s="28" t="n"/>
+      <c r="Z42" s="28" t="n"/>
     </row>
     <row r="43" ht="60" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
@@ -5319,12 +5581,12 @@
           <t>10cm</t>
         </is>
       </c>
-      <c r="I43" s="24" t="inlineStr">
+      <c r="I43" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J43" s="27" t="inlineStr">
+      <c r="J43" s="26" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -5382,6 +5644,11 @@
           <t>偏移方向:前偏10cm, 风险等级:中</t>
         </is>
       </c>
+      <c r="V43" s="28" t="n"/>
+      <c r="W43" s="28" t="n"/>
+      <c r="X43" s="28" t="n"/>
+      <c r="Y43" s="28" t="n"/>
+      <c r="Z43" s="28" t="n"/>
     </row>
     <row r="44" ht="60" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
@@ -5394,8 +5661,8 @@
           <t>S6</t>
         </is>
       </c>
-      <c r="C44" s="29" t="n"/>
-      <c r="D44" s="29" t="n"/>
+      <c r="C44" s="11" t="n"/>
+      <c r="D44" s="11" t="n"/>
       <c r="E44" s="4" t="inlineStr">
         <is>
           <t>后偏10cm</t>
@@ -5416,12 +5683,12 @@
           <t>10cm</t>
         </is>
       </c>
-      <c r="I44" s="24" t="inlineStr">
+      <c r="I44" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J44" s="27" t="inlineStr">
+      <c r="J44" s="26" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -5479,6 +5746,11 @@
           <t>偏移方向:后偏10cm, 风险等级:中</t>
         </is>
       </c>
+      <c r="V44" s="28" t="n"/>
+      <c r="W44" s="28" t="n"/>
+      <c r="X44" s="28" t="n"/>
+      <c r="Y44" s="28" t="n"/>
+      <c r="Z44" s="28" t="n"/>
     </row>
     <row r="45" ht="60" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
@@ -5491,8 +5763,8 @@
           <t>S6</t>
         </is>
       </c>
-      <c r="C45" s="29" t="n"/>
-      <c r="D45" s="29" t="n"/>
+      <c r="C45" s="11" t="n"/>
+      <c r="D45" s="11" t="n"/>
       <c r="E45" s="4" t="inlineStr">
         <is>
           <t>左偏10cm</t>
@@ -5513,12 +5785,12 @@
           <t>10cm</t>
         </is>
       </c>
-      <c r="I45" s="24" t="inlineStr">
+      <c r="I45" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J45" s="27" t="inlineStr">
+      <c r="J45" s="26" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -5576,6 +5848,11 @@
           <t>偏移方向:左偏10cm, 风险等级:中</t>
         </is>
       </c>
+      <c r="V45" s="28" t="n"/>
+      <c r="W45" s="28" t="n"/>
+      <c r="X45" s="28" t="n"/>
+      <c r="Y45" s="28" t="n"/>
+      <c r="Z45" s="28" t="n"/>
     </row>
     <row r="46" ht="60" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
@@ -5588,8 +5865,8 @@
           <t>S6</t>
         </is>
       </c>
-      <c r="C46" s="29" t="n"/>
-      <c r="D46" s="29" t="n"/>
+      <c r="C46" s="11" t="n"/>
+      <c r="D46" s="11" t="n"/>
       <c r="E46" s="4" t="inlineStr">
         <is>
           <t>右偏10cm</t>
@@ -5610,12 +5887,12 @@
           <t>10cm</t>
         </is>
       </c>
-      <c r="I46" s="24" t="inlineStr">
+      <c r="I46" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J46" s="27" t="inlineStr">
+      <c r="J46" s="26" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -5673,6 +5950,11 @@
           <t>偏移方向:右偏10cm, 风险等级:中</t>
         </is>
       </c>
+      <c r="V46" s="28" t="n"/>
+      <c r="W46" s="28" t="n"/>
+      <c r="X46" s="28" t="n"/>
+      <c r="Y46" s="28" t="n"/>
+      <c r="Z46" s="28" t="n"/>
     </row>
     <row r="47" ht="60" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
@@ -5685,8 +5967,8 @@
           <t>S6</t>
         </is>
       </c>
-      <c r="C47" s="29" t="n"/>
-      <c r="D47" s="29" t="n"/>
+      <c r="C47" s="11" t="n"/>
+      <c r="D47" s="11" t="n"/>
       <c r="E47" s="4" t="inlineStr">
         <is>
           <t>左偏3°</t>
@@ -5707,12 +5989,12 @@
           <t>3°</t>
         </is>
       </c>
-      <c r="I47" s="28" t="inlineStr">
+      <c r="I47" s="27" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="J47" s="26" t="inlineStr">
+      <c r="J47" s="25" t="inlineStr">
         <is>
           <t>低</t>
         </is>
@@ -5770,6 +6052,11 @@
           <t>偏移方向:左偏3°, 风险等级:低</t>
         </is>
       </c>
+      <c r="V47" s="28" t="n"/>
+      <c r="W47" s="28" t="n"/>
+      <c r="X47" s="28" t="n"/>
+      <c r="Y47" s="28" t="n"/>
+      <c r="Z47" s="28" t="n"/>
     </row>
     <row r="48" ht="60" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
@@ -5782,8 +6069,8 @@
           <t>S6</t>
         </is>
       </c>
-      <c r="C48" s="30" t="n"/>
-      <c r="D48" s="30" t="n"/>
+      <c r="C48" s="12" t="n"/>
+      <c r="D48" s="12" t="n"/>
       <c r="E48" s="4" t="inlineStr">
         <is>
           <t>右偏3°</t>
@@ -5804,12 +6091,12 @@
           <t>3°</t>
         </is>
       </c>
-      <c r="I48" s="28" t="inlineStr">
+      <c r="I48" s="27" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="J48" s="26" t="inlineStr">
+      <c r="J48" s="25" t="inlineStr">
         <is>
           <t>低</t>
         </is>
@@ -5867,6 +6154,11 @@
           <t>偏移方向:右偏3°, 风险等级:低</t>
         </is>
       </c>
+      <c r="V48" s="28" t="n"/>
+      <c r="W48" s="28" t="n"/>
+      <c r="X48" s="28" t="n"/>
+      <c r="Y48" s="28" t="n"/>
+      <c r="Z48" s="28" t="n"/>
     </row>
     <row r="49" ht="60" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
@@ -5909,12 +6201,12 @@
           <t>10cm</t>
         </is>
       </c>
-      <c r="I49" s="24" t="inlineStr">
+      <c r="I49" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J49" s="27" t="inlineStr">
+      <c r="J49" s="26" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -5972,6 +6264,11 @@
           <t>偏移方向:前偏10cm, 风险等级:中</t>
         </is>
       </c>
+      <c r="V49" s="28" t="n"/>
+      <c r="W49" s="28" t="n"/>
+      <c r="X49" s="28" t="n"/>
+      <c r="Y49" s="28" t="n"/>
+      <c r="Z49" s="28" t="n"/>
     </row>
     <row r="50" ht="60" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
@@ -5984,8 +6281,8 @@
           <t>S7</t>
         </is>
       </c>
-      <c r="C50" s="29" t="n"/>
-      <c r="D50" s="29" t="n"/>
+      <c r="C50" s="11" t="n"/>
+      <c r="D50" s="11" t="n"/>
       <c r="E50" s="4" t="inlineStr">
         <is>
           <t>后偏10cm</t>
@@ -6006,12 +6303,12 @@
           <t>10cm</t>
         </is>
       </c>
-      <c r="I50" s="24" t="inlineStr">
+      <c r="I50" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J50" s="27" t="inlineStr">
+      <c r="J50" s="26" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -6069,6 +6366,11 @@
           <t>偏移方向:后偏10cm, 风险等级:中</t>
         </is>
       </c>
+      <c r="V50" s="28" t="n"/>
+      <c r="W50" s="28" t="n"/>
+      <c r="X50" s="28" t="n"/>
+      <c r="Y50" s="28" t="n"/>
+      <c r="Z50" s="28" t="n"/>
     </row>
     <row r="51" ht="60" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
@@ -6081,8 +6383,8 @@
           <t>S7</t>
         </is>
       </c>
-      <c r="C51" s="29" t="n"/>
-      <c r="D51" s="29" t="n"/>
+      <c r="C51" s="11" t="n"/>
+      <c r="D51" s="11" t="n"/>
       <c r="E51" s="4" t="inlineStr">
         <is>
           <t>左偏10cm</t>
@@ -6103,12 +6405,12 @@
           <t>10cm</t>
         </is>
       </c>
-      <c r="I51" s="24" t="inlineStr">
+      <c r="I51" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J51" s="27" t="inlineStr">
+      <c r="J51" s="26" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -6166,6 +6468,11 @@
           <t>偏移方向:左偏10cm, 风险等级:中</t>
         </is>
       </c>
+      <c r="V51" s="28" t="n"/>
+      <c r="W51" s="28" t="n"/>
+      <c r="X51" s="28" t="n"/>
+      <c r="Y51" s="28" t="n"/>
+      <c r="Z51" s="28" t="n"/>
     </row>
     <row r="52" ht="60" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
@@ -6178,8 +6485,8 @@
           <t>S7</t>
         </is>
       </c>
-      <c r="C52" s="29" t="n"/>
-      <c r="D52" s="29" t="n"/>
+      <c r="C52" s="11" t="n"/>
+      <c r="D52" s="11" t="n"/>
       <c r="E52" s="4" t="inlineStr">
         <is>
           <t>右偏10cm</t>
@@ -6200,12 +6507,12 @@
           <t>10cm</t>
         </is>
       </c>
-      <c r="I52" s="24" t="inlineStr">
+      <c r="I52" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J52" s="27" t="inlineStr">
+      <c r="J52" s="26" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -6263,6 +6570,11 @@
           <t>偏移方向:右偏10cm, 风险等级:中</t>
         </is>
       </c>
+      <c r="V52" s="28" t="n"/>
+      <c r="W52" s="28" t="n"/>
+      <c r="X52" s="28" t="n"/>
+      <c r="Y52" s="28" t="n"/>
+      <c r="Z52" s="28" t="n"/>
     </row>
     <row r="53" ht="60" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
@@ -6275,8 +6587,8 @@
           <t>S7</t>
         </is>
       </c>
-      <c r="C53" s="29" t="n"/>
-      <c r="D53" s="29" t="n"/>
+      <c r="C53" s="11" t="n"/>
+      <c r="D53" s="11" t="n"/>
       <c r="E53" s="4" t="inlineStr">
         <is>
           <t>左偏3°</t>
@@ -6297,12 +6609,12 @@
           <t>3°</t>
         </is>
       </c>
-      <c r="I53" s="24" t="inlineStr">
+      <c r="I53" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J53" s="26" t="inlineStr">
+      <c r="J53" s="25" t="inlineStr">
         <is>
           <t>低</t>
         </is>
@@ -6360,6 +6672,11 @@
           <t>偏移方向:左偏3°, 风险等级:低</t>
         </is>
       </c>
+      <c r="V53" s="28" t="n"/>
+      <c r="W53" s="28" t="n"/>
+      <c r="X53" s="28" t="n"/>
+      <c r="Y53" s="28" t="n"/>
+      <c r="Z53" s="28" t="n"/>
     </row>
     <row r="54" ht="60" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
@@ -6372,8 +6689,8 @@
           <t>S7</t>
         </is>
       </c>
-      <c r="C54" s="30" t="n"/>
-      <c r="D54" s="30" t="n"/>
+      <c r="C54" s="12" t="n"/>
+      <c r="D54" s="12" t="n"/>
       <c r="E54" s="4" t="inlineStr">
         <is>
           <t>右偏3°</t>
@@ -6394,12 +6711,12 @@
           <t>3°</t>
         </is>
       </c>
-      <c r="I54" s="24" t="inlineStr">
+      <c r="I54" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J54" s="26" t="inlineStr">
+      <c r="J54" s="25" t="inlineStr">
         <is>
           <t>低</t>
         </is>
@@ -6457,6 +6774,11 @@
           <t>偏移方向:右偏3°, 风险等级:低</t>
         </is>
       </c>
+      <c r="V54" s="28" t="n"/>
+      <c r="W54" s="28" t="n"/>
+      <c r="X54" s="28" t="n"/>
+      <c r="Y54" s="28" t="n"/>
+      <c r="Z54" s="28" t="n"/>
     </row>
     <row r="55" ht="60" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
@@ -6499,12 +6821,12 @@
           <t>10cm</t>
         </is>
       </c>
-      <c r="I55" s="24" t="inlineStr">
+      <c r="I55" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J55" s="25" t="inlineStr">
+      <c r="J55" s="24" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -6562,6 +6884,11 @@
           <t>偏移方向:前偏10cm, 风险等级:高</t>
         </is>
       </c>
+      <c r="V55" s="28" t="n"/>
+      <c r="W55" s="28" t="n"/>
+      <c r="X55" s="28" t="n"/>
+      <c r="Y55" s="28" t="n"/>
+      <c r="Z55" s="28" t="n"/>
     </row>
     <row r="56" ht="60" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
@@ -6574,8 +6901,8 @@
           <t>S8</t>
         </is>
       </c>
-      <c r="C56" s="29" t="n"/>
-      <c r="D56" s="29" t="n"/>
+      <c r="C56" s="11" t="n"/>
+      <c r="D56" s="11" t="n"/>
       <c r="E56" s="4" t="inlineStr">
         <is>
           <t>后偏10cm</t>
@@ -6596,12 +6923,12 @@
           <t>10cm</t>
         </is>
       </c>
-      <c r="I56" s="24" t="inlineStr">
+      <c r="I56" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J56" s="25" t="inlineStr">
+      <c r="J56" s="24" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -6659,6 +6986,11 @@
           <t>偏移方向:后偏10cm, 风险等级:高</t>
         </is>
       </c>
+      <c r="V56" s="28" t="n"/>
+      <c r="W56" s="28" t="n"/>
+      <c r="X56" s="28" t="n"/>
+      <c r="Y56" s="28" t="n"/>
+      <c r="Z56" s="28" t="n"/>
     </row>
     <row r="57" ht="60" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
@@ -6671,8 +7003,8 @@
           <t>S8</t>
         </is>
       </c>
-      <c r="C57" s="29" t="n"/>
-      <c r="D57" s="29" t="n"/>
+      <c r="C57" s="11" t="n"/>
+      <c r="D57" s="11" t="n"/>
       <c r="E57" s="4" t="inlineStr">
         <is>
           <t>左偏10cm</t>
@@ -6693,12 +7025,12 @@
           <t>10cm</t>
         </is>
       </c>
-      <c r="I57" s="24" t="inlineStr">
+      <c r="I57" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J57" s="25" t="inlineStr">
+      <c r="J57" s="24" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -6756,6 +7088,11 @@
           <t>偏移方向:左偏10cm, 风险等级:高</t>
         </is>
       </c>
+      <c r="V57" s="28" t="n"/>
+      <c r="W57" s="28" t="n"/>
+      <c r="X57" s="28" t="n"/>
+      <c r="Y57" s="28" t="n"/>
+      <c r="Z57" s="28" t="n"/>
     </row>
     <row r="58" ht="60" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
@@ -6768,8 +7105,8 @@
           <t>S8</t>
         </is>
       </c>
-      <c r="C58" s="29" t="n"/>
-      <c r="D58" s="29" t="n"/>
+      <c r="C58" s="11" t="n"/>
+      <c r="D58" s="11" t="n"/>
       <c r="E58" s="4" t="inlineStr">
         <is>
           <t>右偏10cm</t>
@@ -6790,12 +7127,12 @@
           <t>10cm</t>
         </is>
       </c>
-      <c r="I58" s="24" t="inlineStr">
+      <c r="I58" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J58" s="25" t="inlineStr">
+      <c r="J58" s="24" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -6853,6 +7190,11 @@
           <t>偏移方向:右偏10cm, 风险等级:高</t>
         </is>
       </c>
+      <c r="V58" s="28" t="n"/>
+      <c r="W58" s="28" t="n"/>
+      <c r="X58" s="28" t="n"/>
+      <c r="Y58" s="28" t="n"/>
+      <c r="Z58" s="28" t="n"/>
     </row>
     <row r="59" ht="60" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
@@ -6865,8 +7207,8 @@
           <t>S8</t>
         </is>
       </c>
-      <c r="C59" s="29" t="n"/>
-      <c r="D59" s="29" t="n"/>
+      <c r="C59" s="11" t="n"/>
+      <c r="D59" s="11" t="n"/>
       <c r="E59" s="4" t="inlineStr">
         <is>
           <t>左偏3°</t>
@@ -6887,12 +7229,12 @@
           <t>3°</t>
         </is>
       </c>
-      <c r="I59" s="24" t="inlineStr">
+      <c r="I59" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J59" s="26" t="inlineStr">
+      <c r="J59" s="25" t="inlineStr">
         <is>
           <t>低</t>
         </is>
@@ -6950,6 +7292,11 @@
           <t>偏移方向:左偏3°, 风险等级:低</t>
         </is>
       </c>
+      <c r="V59" s="28" t="n"/>
+      <c r="W59" s="28" t="n"/>
+      <c r="X59" s="28" t="n"/>
+      <c r="Y59" s="28" t="n"/>
+      <c r="Z59" s="28" t="n"/>
     </row>
     <row r="60" ht="60" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
@@ -6962,8 +7309,8 @@
           <t>S8</t>
         </is>
       </c>
-      <c r="C60" s="30" t="n"/>
-      <c r="D60" s="30" t="n"/>
+      <c r="C60" s="12" t="n"/>
+      <c r="D60" s="12" t="n"/>
       <c r="E60" s="4" t="inlineStr">
         <is>
           <t>右偏3°</t>
@@ -6984,12 +7331,12 @@
           <t>3°</t>
         </is>
       </c>
-      <c r="I60" s="24" t="inlineStr">
+      <c r="I60" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J60" s="26" t="inlineStr">
+      <c r="J60" s="25" t="inlineStr">
         <is>
           <t>低</t>
         </is>
@@ -7047,6 +7394,11 @@
           <t>偏移方向:右偏3°, 风险等级:低</t>
         </is>
       </c>
+      <c r="V60" s="28" t="n"/>
+      <c r="W60" s="28" t="n"/>
+      <c r="X60" s="28" t="n"/>
+      <c r="Y60" s="28" t="n"/>
+      <c r="Z60" s="28" t="n"/>
     </row>
     <row r="61" ht="60" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
@@ -7089,12 +7441,12 @@
           <t>10cm</t>
         </is>
       </c>
-      <c r="I61" s="24" t="inlineStr">
+      <c r="I61" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J61" s="27" t="inlineStr">
+      <c r="J61" s="26" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -7152,6 +7504,11 @@
           <t>偏移方向:前偏10cm, 风险等级:中</t>
         </is>
       </c>
+      <c r="V61" s="28" t="n"/>
+      <c r="W61" s="28" t="n"/>
+      <c r="X61" s="28" t="n"/>
+      <c r="Y61" s="28" t="n"/>
+      <c r="Z61" s="28" t="n"/>
     </row>
     <row r="62" ht="60" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
@@ -7164,8 +7521,8 @@
           <t>S9</t>
         </is>
       </c>
-      <c r="C62" s="29" t="n"/>
-      <c r="D62" s="29" t="n"/>
+      <c r="C62" s="11" t="n"/>
+      <c r="D62" s="11" t="n"/>
       <c r="E62" s="4" t="inlineStr">
         <is>
           <t>后偏10cm</t>
@@ -7186,12 +7543,12 @@
           <t>10cm</t>
         </is>
       </c>
-      <c r="I62" s="24" t="inlineStr">
+      <c r="I62" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J62" s="27" t="inlineStr">
+      <c r="J62" s="26" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -7249,6 +7606,11 @@
           <t>偏移方向:后偏10cm, 风险等级:中</t>
         </is>
       </c>
+      <c r="V62" s="28" t="n"/>
+      <c r="W62" s="28" t="n"/>
+      <c r="X62" s="28" t="n"/>
+      <c r="Y62" s="28" t="n"/>
+      <c r="Z62" s="28" t="n"/>
     </row>
     <row r="63" ht="60" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
@@ -7261,8 +7623,8 @@
           <t>S9</t>
         </is>
       </c>
-      <c r="C63" s="29" t="n"/>
-      <c r="D63" s="29" t="n"/>
+      <c r="C63" s="11" t="n"/>
+      <c r="D63" s="11" t="n"/>
       <c r="E63" s="4" t="inlineStr">
         <is>
           <t>左偏10cm</t>
@@ -7283,12 +7645,12 @@
           <t>10cm</t>
         </is>
       </c>
-      <c r="I63" s="24" t="inlineStr">
+      <c r="I63" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J63" s="27" t="inlineStr">
+      <c r="J63" s="26" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -7346,6 +7708,11 @@
           <t>偏移方向:左偏10cm, 风险等级:中</t>
         </is>
       </c>
+      <c r="V63" s="28" t="n"/>
+      <c r="W63" s="28" t="n"/>
+      <c r="X63" s="28" t="n"/>
+      <c r="Y63" s="28" t="n"/>
+      <c r="Z63" s="28" t="n"/>
     </row>
     <row r="64" ht="60" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
@@ -7358,8 +7725,8 @@
           <t>S9</t>
         </is>
       </c>
-      <c r="C64" s="29" t="n"/>
-      <c r="D64" s="29" t="n"/>
+      <c r="C64" s="11" t="n"/>
+      <c r="D64" s="11" t="n"/>
       <c r="E64" s="4" t="inlineStr">
         <is>
           <t>右偏10cm</t>
@@ -7380,12 +7747,12 @@
           <t>10cm</t>
         </is>
       </c>
-      <c r="I64" s="24" t="inlineStr">
+      <c r="I64" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J64" s="27" t="inlineStr">
+      <c r="J64" s="26" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -7443,6 +7810,11 @@
           <t>偏移方向:右偏10cm, 风险等级:中</t>
         </is>
       </c>
+      <c r="V64" s="28" t="n"/>
+      <c r="W64" s="28" t="n"/>
+      <c r="X64" s="28" t="n"/>
+      <c r="Y64" s="28" t="n"/>
+      <c r="Z64" s="28" t="n"/>
     </row>
     <row r="65" ht="60" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
@@ -7455,8 +7827,8 @@
           <t>S9</t>
         </is>
       </c>
-      <c r="C65" s="29" t="n"/>
-      <c r="D65" s="29" t="n"/>
+      <c r="C65" s="11" t="n"/>
+      <c r="D65" s="11" t="n"/>
       <c r="E65" s="4" t="inlineStr">
         <is>
           <t>左偏3°</t>
@@ -7477,12 +7849,12 @@
           <t>3°</t>
         </is>
       </c>
-      <c r="I65" s="24" t="inlineStr">
+      <c r="I65" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J65" s="26" t="inlineStr">
+      <c r="J65" s="25" t="inlineStr">
         <is>
           <t>低</t>
         </is>
@@ -7540,6 +7912,11 @@
           <t>偏移方向:左偏3°, 风险等级:低</t>
         </is>
       </c>
+      <c r="V65" s="28" t="n"/>
+      <c r="W65" s="28" t="n"/>
+      <c r="X65" s="28" t="n"/>
+      <c r="Y65" s="28" t="n"/>
+      <c r="Z65" s="28" t="n"/>
     </row>
     <row r="66" ht="60" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
@@ -7552,8 +7929,8 @@
           <t>S9</t>
         </is>
       </c>
-      <c r="C66" s="30" t="n"/>
-      <c r="D66" s="30" t="n"/>
+      <c r="C66" s="12" t="n"/>
+      <c r="D66" s="12" t="n"/>
       <c r="E66" s="4" t="inlineStr">
         <is>
           <t>右偏3°</t>
@@ -7574,12 +7951,12 @@
           <t>3°</t>
         </is>
       </c>
-      <c r="I66" s="24" t="inlineStr">
+      <c r="I66" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J66" s="26" t="inlineStr">
+      <c r="J66" s="25" t="inlineStr">
         <is>
           <t>低</t>
         </is>
@@ -7637,6 +8014,11 @@
           <t>偏移方向:右偏3°, 风险等级:低</t>
         </is>
       </c>
+      <c r="V66" s="28" t="n"/>
+      <c r="W66" s="28" t="n"/>
+      <c r="X66" s="28" t="n"/>
+      <c r="Y66" s="28" t="n"/>
+      <c r="Z66" s="28" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:U66"/>
@@ -7681,7 +8063,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="7"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -7989,7 +8371,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F35"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -8006,7 +8388,7 @@
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>按优先级统计</t>
         </is>
@@ -8111,7 +8493,7 @@
       <c r="D8" s="10" t="inlineStr"/>
     </row>
     <row r="10" ht="16.5" customHeight="1">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>按风险等级统计</t>
         </is>
@@ -8195,7 +8577,7 @@
       </c>
     </row>
     <row r="18" ht="16.5" customHeight="1">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>按货架统计</t>
         </is>
@@ -8426,7 +8808,7 @@
       </c>
     </row>
     <row r="28" ht="16.5" customHeight="1">
-      <c r="A28" s="18" t="inlineStr">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>按偏移类型统计</t>
         </is>
@@ -8594,7 +8976,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:P66"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="3"/>
@@ -9094,7 +9476,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr">
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -9110,7 +9492,7 @@
           <t>TC-OFF-011</t>
         </is>
       </c>
-      <c r="B14" s="29" t="n"/>
+      <c r="B14" s="11" t="n"/>
       <c r="C14" s="10" t="inlineStr">
         <is>
           <t>0.76×0.5m</t>
@@ -9126,7 +9508,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr">
+      <c r="F14" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -9142,7 +9524,7 @@
           <t>TC-OFF-012</t>
         </is>
       </c>
-      <c r="B15" s="29" t="n"/>
+      <c r="B15" s="11" t="n"/>
       <c r="C15" s="10" t="inlineStr">
         <is>
           <t>0.76×0.5m</t>
@@ -9158,7 +9540,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="F15" s="12" t="inlineStr">
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -9174,7 +9556,7 @@
           <t>TC-OFF-013</t>
         </is>
       </c>
-      <c r="B16" s="29" t="n"/>
+      <c r="B16" s="11" t="n"/>
       <c r="C16" s="10" t="inlineStr">
         <is>
           <t>0.76×0.5m</t>
@@ -9190,7 +9572,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
+      <c r="F16" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -9206,7 +9588,7 @@
           <t>TC-OFF-014</t>
         </is>
       </c>
-      <c r="B17" s="29" t="n"/>
+      <c r="B17" s="11" t="n"/>
       <c r="C17" s="10" t="inlineStr">
         <is>
           <t>0.76×0.5m</t>
@@ -9238,7 +9620,7 @@
           <t>TC-OFF-015</t>
         </is>
       </c>
-      <c r="B18" s="30" t="n"/>
+      <c r="B18" s="12" t="n"/>
       <c r="C18" s="10" t="inlineStr">
         <is>
           <t>0.76×0.5m</t>
@@ -9290,7 +9672,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F19" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -9306,7 +9688,7 @@
           <t>TC-OFF-017</t>
         </is>
       </c>
-      <c r="B20" s="29" t="n"/>
+      <c r="B20" s="11" t="n"/>
       <c r="C20" s="10" t="inlineStr">
         <is>
           <t>0.8×0.85m</t>
@@ -9322,7 +9704,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="F20" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -9338,7 +9720,7 @@
           <t>TC-OFF-018</t>
         </is>
       </c>
-      <c r="B21" s="29" t="n"/>
+      <c r="B21" s="11" t="n"/>
       <c r="C21" s="10" t="inlineStr">
         <is>
           <t>0.8×0.85m</t>
@@ -9354,7 +9736,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="F21" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -9370,7 +9752,7 @@
           <t>TC-OFF-019</t>
         </is>
       </c>
-      <c r="B22" s="29" t="n"/>
+      <c r="B22" s="11" t="n"/>
       <c r="C22" s="10" t="inlineStr">
         <is>
           <t>0.8×0.85m</t>
@@ -9386,7 +9768,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F22" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -9402,7 +9784,7 @@
           <t>TC-OFF-020</t>
         </is>
       </c>
-      <c r="B23" s="29" t="n"/>
+      <c r="B23" s="11" t="n"/>
       <c r="C23" s="10" t="inlineStr">
         <is>
           <t>0.8×0.85m</t>
@@ -9434,7 +9816,7 @@
           <t>TC-OFF-021</t>
         </is>
       </c>
-      <c r="B24" s="30" t="n"/>
+      <c r="B24" s="12" t="n"/>
       <c r="C24" s="10" t="inlineStr">
         <is>
           <t>0.8×0.85m</t>
@@ -9486,7 +9868,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="F25" s="16" t="inlineStr">
+      <c r="F25" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -9502,7 +9884,7 @@
           <t>TC-OFF-023</t>
         </is>
       </c>
-      <c r="B26" s="29" t="n"/>
+      <c r="B26" s="11" t="n"/>
       <c r="C26" s="10" t="inlineStr">
         <is>
           <t>0.85×0.8m</t>
@@ -9518,7 +9900,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="F26" s="16" t="inlineStr">
+      <c r="F26" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -9534,7 +9916,7 @@
           <t>TC-OFF-024</t>
         </is>
       </c>
-      <c r="B27" s="29" t="n"/>
+      <c r="B27" s="11" t="n"/>
       <c r="C27" s="10" t="inlineStr">
         <is>
           <t>0.85×0.8m</t>
@@ -9550,7 +9932,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="F27" s="16" t="inlineStr">
+      <c r="F27" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -9566,7 +9948,7 @@
           <t>TC-OFF-025</t>
         </is>
       </c>
-      <c r="B28" s="29" t="n"/>
+      <c r="B28" s="11" t="n"/>
       <c r="C28" s="10" t="inlineStr">
         <is>
           <t>0.85×0.8m</t>
@@ -9582,7 +9964,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="F28" s="16" t="inlineStr">
+      <c r="F28" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -9598,7 +9980,7 @@
           <t>TC-OFF-026</t>
         </is>
       </c>
-      <c r="B29" s="29" t="n"/>
+      <c r="B29" s="11" t="n"/>
       <c r="C29" s="10" t="inlineStr">
         <is>
           <t>0.85×0.8m</t>
@@ -9630,7 +10012,7 @@
           <t>TC-OFF-027</t>
         </is>
       </c>
-      <c r="B30" s="30" t="n"/>
+      <c r="B30" s="12" t="n"/>
       <c r="C30" s="10" t="inlineStr">
         <is>
           <t>0.85×0.8m</t>
@@ -9682,7 +10064,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="F31" s="16" t="inlineStr">
+      <c r="F31" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -9698,7 +10080,7 @@
           <t>TC-OFF-029</t>
         </is>
       </c>
-      <c r="B32" s="29" t="n"/>
+      <c r="B32" s="11" t="n"/>
       <c r="C32" s="10" t="inlineStr">
         <is>
           <t>1.2×0.5m</t>
@@ -9714,7 +10096,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="F32" s="16" t="inlineStr">
+      <c r="F32" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -9730,7 +10112,7 @@
           <t>TC-OFF-030</t>
         </is>
       </c>
-      <c r="B33" s="29" t="n"/>
+      <c r="B33" s="11" t="n"/>
       <c r="C33" s="10" t="inlineStr">
         <is>
           <t>1.2×0.5m</t>
@@ -9746,7 +10128,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="F33" s="16" t="inlineStr">
+      <c r="F33" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -9762,7 +10144,7 @@
           <t>TC-OFF-031</t>
         </is>
       </c>
-      <c r="B34" s="29" t="n"/>
+      <c r="B34" s="11" t="n"/>
       <c r="C34" s="10" t="inlineStr">
         <is>
           <t>1.2×0.5m</t>
@@ -9778,7 +10160,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="F34" s="16" t="inlineStr">
+      <c r="F34" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -9794,7 +10176,7 @@
           <t>TC-OFF-032</t>
         </is>
       </c>
-      <c r="B35" s="29" t="n"/>
+      <c r="B35" s="11" t="n"/>
       <c r="C35" s="10" t="inlineStr">
         <is>
           <t>1.2×0.5m</t>
@@ -9826,7 +10208,7 @@
           <t>TC-OFF-033</t>
         </is>
       </c>
-      <c r="B36" s="30" t="n"/>
+      <c r="B36" s="12" t="n"/>
       <c r="C36" s="10" t="inlineStr">
         <is>
           <t>1.2×0.5m</t>
@@ -9878,7 +10260,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="F37" s="16" t="inlineStr">
+      <c r="F37" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -9894,7 +10276,7 @@
           <t>TC-OFF-035</t>
         </is>
       </c>
-      <c r="B38" s="29" t="n"/>
+      <c r="B38" s="11" t="n"/>
       <c r="C38" s="10" t="inlineStr">
         <is>
           <t>1.1×1.1m</t>
@@ -9910,7 +10292,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="F38" s="16" t="inlineStr">
+      <c r="F38" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -9926,7 +10308,7 @@
           <t>TC-OFF-036</t>
         </is>
       </c>
-      <c r="B39" s="29" t="n"/>
+      <c r="B39" s="11" t="n"/>
       <c r="C39" s="10" t="inlineStr">
         <is>
           <t>1.1×1.1m</t>
@@ -9942,7 +10324,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="F39" s="16" t="inlineStr">
+      <c r="F39" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -9958,7 +10340,7 @@
           <t>TC-OFF-037</t>
         </is>
       </c>
-      <c r="B40" s="29" t="n"/>
+      <c r="B40" s="11" t="n"/>
       <c r="C40" s="10" t="inlineStr">
         <is>
           <t>1.1×1.1m</t>
@@ -9974,7 +10356,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="F40" s="16" t="inlineStr">
+      <c r="F40" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -9990,7 +10372,7 @@
           <t>TC-OFF-038</t>
         </is>
       </c>
-      <c r="B41" s="29" t="n"/>
+      <c r="B41" s="11" t="n"/>
       <c r="C41" s="10" t="inlineStr">
         <is>
           <t>1.1×1.1m</t>
@@ -10022,7 +10404,7 @@
           <t>TC-OFF-039</t>
         </is>
       </c>
-      <c r="B42" s="30" t="n"/>
+      <c r="B42" s="12" t="n"/>
       <c r="C42" s="10" t="inlineStr">
         <is>
           <t>1.1×1.1m</t>
@@ -10074,7 +10456,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="F43" s="16" t="inlineStr">
+      <c r="F43" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -10090,7 +10472,7 @@
           <t>TC-OFF-041</t>
         </is>
       </c>
-      <c r="B44" s="29" t="n"/>
+      <c r="B44" s="11" t="n"/>
       <c r="C44" s="10" t="inlineStr">
         <is>
           <t>1.2×1m</t>
@@ -10106,7 +10488,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="F44" s="16" t="inlineStr">
+      <c r="F44" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -10122,7 +10504,7 @@
           <t>TC-OFF-042</t>
         </is>
       </c>
-      <c r="B45" s="29" t="n"/>
+      <c r="B45" s="11" t="n"/>
       <c r="C45" s="10" t="inlineStr">
         <is>
           <t>1.2×1m</t>
@@ -10138,7 +10520,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="F45" s="16" t="inlineStr">
+      <c r="F45" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -10154,7 +10536,7 @@
           <t>TC-OFF-043</t>
         </is>
       </c>
-      <c r="B46" s="29" t="n"/>
+      <c r="B46" s="11" t="n"/>
       <c r="C46" s="10" t="inlineStr">
         <is>
           <t>1.2×1m</t>
@@ -10170,7 +10552,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="F46" s="16" t="inlineStr">
+      <c r="F46" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -10186,7 +10568,7 @@
           <t>TC-OFF-044</t>
         </is>
       </c>
-      <c r="B47" s="29" t="n"/>
+      <c r="B47" s="11" t="n"/>
       <c r="C47" s="10" t="inlineStr">
         <is>
           <t>1.2×1m</t>
@@ -10218,7 +10600,7 @@
           <t>TC-OFF-045</t>
         </is>
       </c>
-      <c r="B48" s="30" t="n"/>
+      <c r="B48" s="12" t="n"/>
       <c r="C48" s="10" t="inlineStr">
         <is>
           <t>1.2×1m</t>
@@ -10270,7 +10652,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="F49" s="16" t="inlineStr">
+      <c r="F49" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -10286,7 +10668,7 @@
           <t>TC-OFF-047</t>
         </is>
       </c>
-      <c r="B50" s="29" t="n"/>
+      <c r="B50" s="11" t="n"/>
       <c r="C50" s="10" t="inlineStr">
         <is>
           <t>1×1.2m</t>
@@ -10302,7 +10684,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="F50" s="16" t="inlineStr">
+      <c r="F50" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -10318,7 +10700,7 @@
           <t>TC-OFF-048</t>
         </is>
       </c>
-      <c r="B51" s="29" t="n"/>
+      <c r="B51" s="11" t="n"/>
       <c r="C51" s="10" t="inlineStr">
         <is>
           <t>1×1.2m</t>
@@ -10334,7 +10716,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="F51" s="16" t="inlineStr">
+      <c r="F51" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -10350,7 +10732,7 @@
           <t>TC-OFF-049</t>
         </is>
       </c>
-      <c r="B52" s="29" t="n"/>
+      <c r="B52" s="11" t="n"/>
       <c r="C52" s="10" t="inlineStr">
         <is>
           <t>1×1.2m</t>
@@ -10366,7 +10748,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="F52" s="16" t="inlineStr">
+      <c r="F52" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -10382,7 +10764,7 @@
           <t>TC-OFF-050</t>
         </is>
       </c>
-      <c r="B53" s="29" t="n"/>
+      <c r="B53" s="11" t="n"/>
       <c r="C53" s="10" t="inlineStr">
         <is>
           <t>1×1.2m</t>
@@ -10414,7 +10796,7 @@
           <t>TC-OFF-051</t>
         </is>
       </c>
-      <c r="B54" s="30" t="n"/>
+      <c r="B54" s="12" t="n"/>
       <c r="C54" s="10" t="inlineStr">
         <is>
           <t>1×1.2m</t>
@@ -10466,7 +10848,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="F55" s="12" t="inlineStr">
+      <c r="F55" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -10482,7 +10864,7 @@
           <t>TC-OFF-053</t>
         </is>
       </c>
-      <c r="B56" s="29" t="n"/>
+      <c r="B56" s="11" t="n"/>
       <c r="C56" s="10" t="inlineStr">
         <is>
           <t>0.76×0.5m</t>
@@ -10498,7 +10880,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="F56" s="12" t="inlineStr">
+      <c r="F56" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -10514,7 +10896,7 @@
           <t>TC-OFF-054</t>
         </is>
       </c>
-      <c r="B57" s="29" t="n"/>
+      <c r="B57" s="11" t="n"/>
       <c r="C57" s="10" t="inlineStr">
         <is>
           <t>0.76×0.5m</t>
@@ -10530,7 +10912,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="F57" s="12" t="inlineStr">
+      <c r="F57" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -10546,7 +10928,7 @@
           <t>TC-OFF-055</t>
         </is>
       </c>
-      <c r="B58" s="29" t="n"/>
+      <c r="B58" s="11" t="n"/>
       <c r="C58" s="10" t="inlineStr">
         <is>
           <t>0.76×0.5m</t>
@@ -10562,7 +10944,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="F58" s="12" t="inlineStr">
+      <c r="F58" s="13" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -10578,7 +10960,7 @@
           <t>TC-OFF-056</t>
         </is>
       </c>
-      <c r="B59" s="29" t="n"/>
+      <c r="B59" s="11" t="n"/>
       <c r="C59" s="10" t="inlineStr">
         <is>
           <t>0.76×0.5m</t>
@@ -10610,7 +10992,7 @@
           <t>TC-OFF-057</t>
         </is>
       </c>
-      <c r="B60" s="30" t="n"/>
+      <c r="B60" s="12" t="n"/>
       <c r="C60" s="10" t="inlineStr">
         <is>
           <t>0.76×0.5m</t>
@@ -10662,7 +11044,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="F61" s="16" t="inlineStr">
+      <c r="F61" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -10678,7 +11060,7 @@
           <t>TC-OFF-059</t>
         </is>
       </c>
-      <c r="B62" s="29" t="n"/>
+      <c r="B62" s="11" t="n"/>
       <c r="C62" s="10" t="inlineStr">
         <is>
           <t>1.2×0.5m</t>
@@ -10694,7 +11076,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="F62" s="16" t="inlineStr">
+      <c r="F62" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -10710,7 +11092,7 @@
           <t>TC-OFF-060</t>
         </is>
       </c>
-      <c r="B63" s="29" t="n"/>
+      <c r="B63" s="11" t="n"/>
       <c r="C63" s="10" t="inlineStr">
         <is>
           <t>1.2×0.5m</t>
@@ -10726,7 +11108,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="F63" s="16" t="inlineStr">
+      <c r="F63" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -10742,7 +11124,7 @@
           <t>TC-OFF-061</t>
         </is>
       </c>
-      <c r="B64" s="29" t="n"/>
+      <c r="B64" s="11" t="n"/>
       <c r="C64" s="10" t="inlineStr">
         <is>
           <t>1.2×0.5m</t>
@@ -10758,7 +11140,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="F64" s="16" t="inlineStr">
+      <c r="F64" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -10774,7 +11156,7 @@
           <t>TC-OFF-062</t>
         </is>
       </c>
-      <c r="B65" s="29" t="n"/>
+      <c r="B65" s="11" t="n"/>
       <c r="C65" s="10" t="inlineStr">
         <is>
           <t>1.2×0.5m</t>
@@ -10806,7 +11188,7 @@
           <t>TC-OFF-063</t>
         </is>
       </c>
-      <c r="B66" s="30" t="n"/>
+      <c r="B66" s="12" t="n"/>
       <c r="C66" s="10" t="inlineStr">
         <is>
           <t>1.2×0.5m</t>
@@ -10865,7 +11247,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D31"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>

--- a/testcases/货架偏移容差测试用例.xlsx
+++ b/testcases/货架偏移容差测试用例.xlsx
@@ -1541,7 +1541,11 @@
           <t>12138</t>
         </is>
       </c>
-      <c r="R4" s="20" t="inlineStr"/>
+      <c r="R4" s="20" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="S4" s="20" t="inlineStr"/>
       <c r="T4" s="20" t="inlineStr"/>
       <c r="U4" s="20" t="inlineStr">
@@ -1554,17 +1558,17 @@
           <t>通过</t>
         </is>
       </c>
-      <c r="W4" s="28" t="inlineStr">
+      <c r="W4" s="20" t="inlineStr">
         <is>
           <t>吴晓峰</t>
         </is>
       </c>
-      <c r="X4" s="28" t="n"/>
-      <c r="Y4" s="28" t="n"/>
-      <c r="Z4" s="28" t="n"/>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2026-07-06 01:09:56</t>
+      <c r="X4" s="20" t="inlineStr"/>
+      <c r="Y4" s="20" t="inlineStr"/>
+      <c r="Z4" s="20" t="inlineStr"/>
+      <c r="AA4" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-07 23:06:01</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1665,11 @@
           <t>12</t>
         </is>
       </c>
-      <c r="R5" s="20" t="inlineStr"/>
+      <c r="R5" s="20" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
       <c r="S5" s="20" t="inlineStr"/>
       <c r="T5" s="20" t="inlineStr"/>
       <c r="U5" s="20" t="inlineStr">
@@ -1674,13 +1682,17 @@
           <t>通过</t>
         </is>
       </c>
-      <c r="W5" s="28" t="inlineStr"/>
-      <c r="X5" s="28" t="inlineStr"/>
-      <c r="Y5" s="28" t="inlineStr"/>
-      <c r="Z5" s="28" t="inlineStr"/>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-07-06 01:30:51</t>
+      <c r="W5" s="20" t="inlineStr"/>
+      <c r="X5" s="20" t="inlineStr"/>
+      <c r="Y5" s="20" t="inlineStr"/>
+      <c r="Z5" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-07 23:06:05</t>
+        </is>
+      </c>
+      <c r="AA5" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-07 23:06:06</t>
         </is>
       </c>
     </row>

--- a/testcases/货架偏移容差测试用例.xlsx
+++ b/testcases/货架偏移容差测试用例.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="19240" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="货架偏移容差测试用例" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="偏移场景说明" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="统计汇总" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试记录表(填写用)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="判定标准与执行说明" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="货架偏移容差测试用例" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="偏移场景说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="统计汇总" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="测试记录表(填写用)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="判定标准与执行说明" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'货架偏移容差测试用例'!$A$3:$U$66</definedName>
@@ -1568,7 +1568,7 @@
       <c r="Z4" s="20" t="inlineStr"/>
       <c r="AA4" s="20" t="inlineStr">
         <is>
-          <t>2026-07-07 23:06:01</t>
+          <t>2026-07-08 00:24:20</t>
         </is>
       </c>
     </row>
